--- a/workspaces/btc_daily_14days/volatility/bb_width_20.xlsx
+++ b/workspaces/btc_daily_14days/volatility/bb_width_20.xlsx
@@ -575,46 +575,46 @@
         <v>140</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.792275965503983</v>
+        <v>1.786299296200418</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2.324118875090186</v>
+        <v>2.316846939079348</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.5003835732132629</v>
+        <v>0.4986661888178361</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.7988617919203165</v>
+        <v>-0.7959894151166367</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.8069663864455734</v>
+        <v>0.8045958546604268</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.755695173315907</v>
+        <v>-1.749893933875065</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-3.986977618226796</v>
+        <v>-3.974144818333137</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-3.740359148873452</v>
+        <v>-3.728461034683583</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-4.518089328708683</v>
+        <v>-4.503706037320697</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-5.371258801411457</v>
+        <v>-5.354076349092672</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-7.009944735047853</v>
+        <v>-6.987510992988689</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-7.693406344619255</v>
+        <v>-7.668805880547374</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-6.683945714084913</v>
+        <v>-6.662634419335447</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-7.151587520050334</v>
+        <v>-7.12883813170999</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>290</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.2651823694451991</v>
+        <v>0.2639302077817689</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.861824184502225</v>
+        <v>4.844678792639478</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.468101210124679</v>
+        <v>4.452081254769404</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.634908182786823</v>
+        <v>5.615253526336041</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3.026227643879643</v>
+        <v>3.015691522970698</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>6.432574720977485</v>
+        <v>6.409957979098493</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.349477466923695</v>
+        <v>6.327084511717729</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.574192315096383</v>
+        <v>6.55083264363028</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.823684574851377</v>
+        <v>5.803005469997927</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.084093212126362</v>
+        <v>8.05547710739782</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>8.918269740397832</v>
+        <v>8.886734023983379</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>10.6845343486566</v>
+        <v>10.64671408296842</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>10.61185970899695</v>
+        <v>10.57420938161452</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>12.24966286801245</v>
+        <v>12.20613723774765</v>
       </c>
     </row>
     <row r="8">
@@ -676,49 +676,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.611826229529939</v>
+        <v>-1.614330289914726</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-3.591762783308816</v>
+        <v>-3.5971944941004</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.338153462748387</v>
+        <v>-2.341400977978552</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.9489819814742404</v>
+        <v>-0.9500107544444347</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.2798088369212692</v>
+        <v>0.2805672473973004</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.3229611693721424</v>
+        <v>0.3242308475374927</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.247520120938759</v>
+        <v>1.250361919472297</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.818672071227851</v>
+        <v>4.827603673777553</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.01206485649476</v>
+        <v>5.021213671482236</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.165648774235812</v>
+        <v>4.173632471158299</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>3.710248293202937</v>
+        <v>3.717557910671296</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3.745571382444965</v>
+        <v>3.753178173496849</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2.822176713978394</v>
+        <v>2.828273896684074</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>3.072357665026139</v>
+        <v>3.079118468651345</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>303</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.668355811959145</v>
+        <v>-1.661902025923148</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.619863418322822</v>
+        <v>-2.609934343025479</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.694600111718024</v>
+        <v>-1.688896030708008</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-2.225077583251405</v>
+        <v>-2.217767010309096</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.113267269502074</v>
+        <v>-1.109977800789729</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.476254619180274</v>
+        <v>-1.472729610464242</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.230768660772597</v>
+        <v>-1.228638253279577</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.359253783060289</v>
+        <v>-2.35483087987356</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.735804226893784</v>
+        <v>-4.72236599423168</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-4.265752369226405</v>
+        <v>-4.25430464472106</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-4.803023172221522</v>
+        <v>-4.789590259635638</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-5.431340139309064</v>
+        <v>-5.41618029521554</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.212026622473715</v>
+        <v>-2.208508363413756</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.629702320084327</v>
+        <v>-1.629073869569822</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>339</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-4.115857199265889</v>
+        <v>-4.097541692765908</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-9.562239071817231</v>
+        <v>-9.520717557218745</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-11.43203403210121</v>
+        <v>-11.38403373378197</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-11.01097783769599</v>
+        <v>-10.96497375935933</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-10.96351319998804</v>
+        <v>-10.91804559299839</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-12.44147334439124</v>
+        <v>-12.39102948818636</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-14.30329141687805</v>
+        <v>-14.24573318505215</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-14.18465344749007</v>
+        <v>-14.12947876875761</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-12.47752507817869</v>
+        <v>-12.42827688952818</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-12.15099277172262</v>
+        <v>-12.10362023486148</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-12.36085026102608</v>
+        <v>-12.31238106441689</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-12.62637122471574</v>
+        <v>-12.5772755418104</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-13.34794407281633</v>
+        <v>-13.29679167314156</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-13.39691149055007</v>
+        <v>-13.34670580975499</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1755575255081396</v>
+        <v>-0.174564734552817</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.524127139673524</v>
+        <v>1.524206919793869</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.1358809496330764</v>
+        <v>0.1372314766874396</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.8738342470537219</v>
+        <v>-0.8715825938548392</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.399560485218657</v>
+        <v>-3.394860458974676</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.43661589912444</v>
+        <v>-3.432019441466693</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.533714832784895</v>
+        <v>-1.530984796503894</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.002156697268632</v>
+        <v>-1.999480971566243</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.064103095876625</v>
+        <v>-2.061250578443641</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.255038741957456</v>
+        <v>-1.253181036869307</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.792634792295026</v>
+        <v>-1.790149462476194</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.09793538989799799</v>
+        <v>-0.09725615601809068</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-3.510380211623563</v>
+        <v>-3.506431067356132</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-5.589726791199666</v>
+        <v>-5.583987633371443</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>279</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.1636892162672368</v>
+        <v>-0.1582848400155896</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.092120683313219</v>
+        <v>1.094679412575061</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.528554474896268</v>
+        <v>-2.508049724887471</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.190416037629277</v>
+        <v>-4.161753108413734</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.297681591648768</v>
+        <v>-3.272320639452097</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.002335572967581</v>
+        <v>-2.979175501696872</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.089233473430632</v>
+        <v>-3.066579481947329</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.91769228601629</v>
+        <v>-3.893570605563667</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.981595519695766</v>
+        <v>-3.956491480339352</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.038437392682354</v>
+        <v>-3.019465054386686</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-5.763980910664593</v>
+        <v>-5.730819448999839</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-4.651982313138298</v>
+        <v>-4.625899312902284</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-5.797874551406714</v>
+        <v>-5.764921052100014</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.469307048022984</v>
+        <v>-4.443226252550048</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.129750085587133</v>
+        <v>1.129746586384059</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.93363540982083</v>
+        <v>1.933614314051198</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.538766703224354</v>
+        <v>1.538824701508375</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.229530888805833</v>
+        <v>-1.229218655325148</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.857586542279044</v>
+        <v>2.857562860763075</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.702918525248563</v>
+        <v>1.702974598117791</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.617376479382408</v>
+        <v>1.617422489138718</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.7857098533313831</v>
+        <v>-0.7855014035224457</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.363309159179515</v>
+        <v>-0.3631226564304839</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.15151205129478</v>
+        <v>-3.151129516168425</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.872860420701265</v>
+        <v>-2.872453840166251</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-7.691131317837709</v>
+        <v>-7.690360762819537</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-4.719484007589649</v>
+        <v>-4.71892772520409</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.987839778295132</v>
+        <v>-3.987367951405183</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>232</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.385872024617562</v>
+        <v>1.384172042422122</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.242942967656994</v>
+        <v>-3.215364300925785</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.534602118849961</v>
+        <v>1.538908387076994</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.526924216974614</v>
+        <v>2.528837525072923</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.2643650708680525</v>
+        <v>0.2772123252461043</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.285849427350406</v>
+        <v>2.286709037759486</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.359057870837617</v>
+        <v>4.347023814693351</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.301778904465827</v>
+        <v>1.305422213485457</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.05646334026623379</v>
+        <v>-0.04441831038531063</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.549173165599271</v>
+        <v>2.545334697619943</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1785491871384863</v>
+        <v>0.1913978243477459</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.251598912245271</v>
+        <v>-3.219686001502865</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.678337283801959</v>
+        <v>-3.643119256214142</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.8281614409475537</v>
+        <v>-0.811104141562538</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-4.123873102818614</v>
+        <v>-4.12273640617628</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.503683718999682</v>
+        <v>3.503433680154288</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.9349019689248337</v>
+        <v>0.9352268248993099</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.0218014202068062</v>
+        <v>-0.02115470094288696</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.647179157018094</v>
+        <v>-1.646183041761226</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-3.213479941183046</v>
+        <v>-3.212230911069199</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-6.023740684595907</v>
+        <v>-6.021994102923124</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.228640654426385</v>
+        <v>-3.227480242212607</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.292005319875535</v>
+        <v>-3.290753687002379</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-6.325649345570191</v>
+        <v>-6.323867682557029</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.261365166150924</v>
+        <v>-3.260032558075515</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.230781984908994</v>
+        <v>-3.229357411405822</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.655306521430788</v>
+        <v>-3.653734422205744</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-5.596693831530764</v>
+        <v>-5.594880286277125</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.493438320210046</v>
+        <v>-2.496655701582441</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.57336636355398</v>
+        <v>-1.576268885777104</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.335323677745514</v>
+        <v>-1.338336742909078</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.470893329948133</v>
+        <v>-2.475307518326041</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.110580367805113</v>
+        <v>-1.114082491364762</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-6.50934096173502</v>
+        <v>-6.516768899753032</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-6.229277801489573</v>
+        <v>-6.236295564113547</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-4.168700721593588</v>
+        <v>-4.173978050167293</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-4.232985277401845</v>
+        <v>-4.238621620641858</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-5.721286324216003</v>
+        <v>-5.727822196257122</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-6.564746222487045</v>
+        <v>-6.57250820503149</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-7.172799102259717</v>
+        <v>-7.181410968286592</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-6.328979556976755</v>
+        <v>-6.337200434409894</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-7.99794827718538</v>
+        <v>-8.00690910532262</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.27579244902094</v>
+        <v>3.27679386605498</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>11.92062909246679</v>
+        <v>11.92954717710202</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>8.320632180742074</v>
+        <v>8.325682162653621</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>7.16883403129814</v>
+        <v>7.171875262349765</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>10.47656666237981</v>
+        <v>10.48278816909338</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>9.491957318044342</v>
+        <v>9.496862338553626</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>4.27901847256679</v>
+        <v>4.279195976324672</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.906437392909922</v>
+        <v>2.905771223850522</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.2812682339724759</v>
+        <v>0.2776153517049522</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.137909998498813</v>
+        <v>-3.144709329965821</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.34476207424801</v>
+        <v>-3.352690002433413</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.386069958559226</v>
+        <v>-1.392725132475952</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.408438490389109</v>
+        <v>1.404225536107013</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.2802355926968119</v>
+        <v>-0.2855201593600896</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.283631743484221</v>
+        <v>2.283837242363717</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.03511545536079552</v>
+        <v>0.0336526031546498</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.455294652509679</v>
+        <v>-5.463730100436592</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-5.325041519902179</v>
+        <v>-5.334653745607262</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-5.226520059815108</v>
+        <v>-5.23554264739775</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.655192771780975</v>
+        <v>-3.663134147933697</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.7186722370615328</v>
+        <v>0.7150544573952686</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.659339187197673</v>
+        <v>-1.665118140490542</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.339331545875829</v>
+        <v>-1.345738436512974</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-4.740128280376666</v>
+        <v>-4.750526801453603</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.396257640879824</v>
+        <v>-2.405341035549263</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>4.020267426453906</v>
+        <v>4.017619787766591</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.679153494510608</v>
+        <v>1.674074596315677</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>4.484476460339238</v>
+        <v>4.482883480011289</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.2875559672687942</v>
+        <v>-0.2932416056232228</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-4.10501193317419</v>
+        <v>-4.118856537973663</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-5.970468875065023</v>
+        <v>-5.993769435430067</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.04213719871916055</v>
+        <v>0.02999677729908967</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.44489245423518</v>
+        <v>2.439870391709839</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>4.212922627244787</v>
+        <v>4.211203362596585</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.3928947923255</v>
+        <v>3.389908701094249</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3.66100551119105</v>
+        <v>3.658773483402044</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>7.276476213244088</v>
+        <v>7.280578318369926</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>6.151103071132972</v>
+        <v>6.150276496054488</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>5.216627842490162</v>
+        <v>5.211305155768351</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>8.193970242317434</v>
+        <v>8.197149601888228</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>4.825787584731074</v>
+        <v>4.820124881783734</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>5.069677438744556</v>
+        <v>5.066929064056879</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-4.534254646740592</v>
+        <v>-4.576484725620091</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.043787443378378</v>
+        <v>-1.065665309387512</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.418247986709595</v>
+        <v>-0.4526514649874471</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.328811180632705</v>
+        <v>-2.378532216423203</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.255216583886956</v>
+        <v>3.245467660330625</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>9.675107501194461</v>
+        <v>9.703087979758351</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>9.590373783922111</v>
+        <v>9.619101832524002</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>9.12319038514061</v>
+        <v>9.149675723628697</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>8.041782335693071</v>
+        <v>8.058366185310859</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>11.27328980372636</v>
+        <v>11.30181951742024</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>10.70184705270867</v>
+        <v>10.71945963114359</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>9.708267413063965</v>
+        <v>9.726684855637913</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>13.39526348765963</v>
+        <v>13.43051466897514</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>9.545805421588128</v>
+        <v>9.56482902587436</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.82677165354324</v>
+        <v>-1.962082783256093</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>7.228321400159096</v>
+        <v>7.335311595746127</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>16.16678602689585</v>
+        <v>16.42724179714806</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>10.96370582616994</v>
+        <v>11.06488659937201</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>15.75861794443118</v>
+        <v>16.03359727064553</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>6.722726548813498</v>
+        <v>6.782515187523863</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>5.30465949820789</v>
+        <v>5.333706610132019</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>10.17080943275972</v>
+        <v>10.32645354081929</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>10.1098095465775</v>
+        <v>10.24366832069411</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>18.59301769488283</v>
+        <v>18.92028182256045</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>23.72159770389858</v>
+        <v>24.14278082679736</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>23.25574578837139</v>
+        <v>23.69444253077511</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>24.20878880116735</v>
+        <v>24.65876626268214</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>22.60836249236286</v>
+        <v>23.03750237709595</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>8.376126897181244</v>
+        <v>8.439864134630149</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>12.56165473349252</v>
+        <v>12.70832757585774</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>12.16678602689583</v>
+        <v>12.27408879052105</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>22.44196669573522</v>
+        <v>22.67530070034014</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>11.75861794443117</v>
+        <v>11.87518425599517</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>9.157509157509146</v>
+        <v>9.231449723122587</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.275673990961515</v>
+        <v>3.264363064673837</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>7.15631667913653</v>
+        <v>7.211260258759481</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>5.646041430635307</v>
+        <v>5.66577681537462</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>6.245191607926301</v>
+        <v>6.272344543732622</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>7.489713645927559</v>
+        <v>7.519652358831408</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>8.97337216559184</v>
+        <v>9.043150847348713</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>9.442341712284183</v>
+        <v>9.512196838534329</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>9.678347504854074</v>
+        <v>9.761918170810688</v>
       </c>
     </row>
     <row r="23">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 0.04388</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4075~4088</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4075</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.02279252764638073</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 0.06395</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3935~3948</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3935</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.08715665860916744</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 0.08403</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3645~3658</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3645</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.1150894957157149</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 0.1041</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3250~3261</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3250</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.06712592388693395</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 0.1242</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2947~2958</t>
-        </is>
+      <c r="B10" t="n">
+        <v>2947</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.2448983937859737</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 0.1443</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2608~2619</t>
-        </is>
+      <c r="B11" t="n">
+        <v>2608</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.8093490031958979</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 0.1643</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2307~2317</t>
-        </is>
+      <c r="B12" t="n">
+        <v>2307</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.9377226638211056</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 0.1844</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2028~2038</t>
-        </is>
+      <c r="B13" t="n">
+        <v>2028</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1.088504761242426</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 0.2045</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1822~1831</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1822</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>1.08384185455791</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 0.2246</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1590~1599</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1590</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>1.040020091297222</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 0.2446</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1407~1415</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1407</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>1.711508676256457</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 0.2647</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1250~1257</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1250</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>2.240054122113023</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 0.2848</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1095~1101</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1095</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>2.093301007673759</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 0.3049</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>939~944</t>
-        </is>
+      <c r="B19" t="n">
+        <v>939</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>2.061646425552738</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.3249</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>804~808</t>
-        </is>
+      <c r="B20" t="n">
+        <v>804</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>2.457056729294976</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.345</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>707~710</t>
-        </is>
+      <c r="B21" t="n">
+        <v>707</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>3.422054637536505</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.3651</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>634~635</t>
-        </is>
+      <c r="B22" t="n">
+        <v>634</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>4.041994750656158</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.3852</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>566~566</t>
-        </is>
+      <c r="B23" t="n">
+        <v>566</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>3.513628817599212</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.4052</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>494~494</t>
-        </is>
+      <c r="B24" t="n">
+        <v>494</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>2.972148724324441</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.4253</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>412~412</t>
-        </is>
+      <c r="B25" t="n">
+        <v>412</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>3.089085951634679</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.4454</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>341~341</t>
-        </is>
+      <c r="B26" t="n">
+        <v>341</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>2.931781621138995</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.4655</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>274~274</t>
-        </is>
+      <c r="B27" t="n">
+        <v>274</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>1.156196716286374</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.4855</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>238~238</t>
-        </is>
+      <c r="B28" t="n">
+        <v>238</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.3925979840755147</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.5056</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>208~208</t>
-        </is>
+      <c r="B29" t="n">
+        <v>208</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-2.012669089440749</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.5257</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>176~176</t>
-        </is>
+      <c r="B30" t="n">
+        <v>176</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-1.925256502028155</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.5458</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>158~158</t>
-        </is>
+      <c r="B31" t="n">
+        <v>158</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-5.025083889830228</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.5658</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>142~142</t>
-        </is>
+      <c r="B32" t="n">
+        <v>142</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-2.493438320209975</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.5859</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>129~129</t>
-        </is>
+      <c r="B33" t="n">
+        <v>129</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-2.105841420985172</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.606</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>105~105</t>
-        </is>
+      <c r="B34" t="n">
+        <v>105</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-2.017247844019501</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.6261</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-6.064866891638545</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 0.04388</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>2.268466441694791</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 0.06395</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>224~224</t>
-        </is>
+      <c r="B7" t="n">
+        <v>224</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>1.970847394075733</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 0.08403</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>514~514</t>
-        </is>
+      <c r="B8" t="n">
+        <v>514</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>1.008507205081855</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 0.1041</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>909~911</t>
-        </is>
+      <c r="B9" t="n">
+        <v>909</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.1333944124163438</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 0.1242</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1212~1214</t>
-        </is>
+      <c r="B10" t="n">
+        <v>1212</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.5165025706218387</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 0.1443</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1551~1553</t>
-        </is>
+      <c r="B11" t="n">
+        <v>1551</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-1.302195564253765</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 0.1643</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1852~1855</t>
-        </is>
+      <c r="B12" t="n">
+        <v>1852</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-1.118775247433689</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 0.1844</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2131~2134</t>
-        </is>
+      <c r="B13" t="n">
+        <v>2131</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.9939069237713625</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 0.2045</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2337~2341</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2337</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.8061252061561532</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 0.2246</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2569~2573</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2569</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.6084791286048485</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 0.2446</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2752~2757</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2752</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.8430937427707335</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 0.2647</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2909~2915</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2909</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.932546381959547</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 0.2848</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3064~3071</t>
-        </is>
+      <c r="B18" t="n">
+        <v>3064</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.7187720877124164</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 0.3049</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3220~3228</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3220</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.5727443920811055</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.3249</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3355~3364</t>
-        </is>
+      <c r="B20" t="n">
+        <v>3355</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.5612147768092655</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.345</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3452~3462</t>
-        </is>
+      <c r="B21" t="n">
+        <v>3452</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.6736809545254019</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.3651</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3525~3537</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3525</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.6981315630711578</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.3852</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3593~3606</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3593</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.5244976657451943</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.4052</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3665~3678</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3665</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.3727205388070374</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.4253</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3747~3760</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3747</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.3125872563801835</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.4454</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3818~3831</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3818</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.2355422095339179</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.4655</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3885~3898</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3885</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.05629106520740379</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.4855</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3921~3934</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3921</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.0485037235114234</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.5056</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3951~3964</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3951</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.1301741924035511</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.5257</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3983~3996</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3983</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.1091642823926264</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.5458</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>4001~4014</t>
-        </is>
+      <c r="B31" t="n">
+        <v>4001</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.2220574446131423</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.5658</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4017~4030</t>
-        </is>
+      <c r="B32" t="n">
+        <v>4017</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.1120207368619788</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.5859</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4030~4043</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4030</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.09127600083875365</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.606</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4054~4067</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4054</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.07602319933760526</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.6261</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4075~4088</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4075</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.1484403490659574</v>

--- a/workspaces/btc_daily_14days/volatility/bb_width_20.xlsx
+++ b/workspaces/btc_daily_14days/volatility/bb_width_20.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that BB Width-20 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that BB Width-20 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -568,157 +568,157 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 0.05392</t>
+          <t>X ≈ 0.054</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>140</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.786299296200418</v>
+        <v>1.769700232973541</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2.316846939079348</v>
+        <v>2.328552855693808</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.4986661888178361</v>
+        <v>0.5114878875682933</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.7959894151166367</v>
+        <v>-0.7835443534116706</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.8045958546604268</v>
+        <v>0.8661131788292522</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.749893933875065</v>
+        <v>-1.712981221684807</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-3.974144818333137</v>
+        <v>-3.913198240657991</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-3.728461034683583</v>
+        <v>-3.666145708831692</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-4.503706037320697</v>
+        <v>-4.417378565424841</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-5.354076349092672</v>
+        <v>-5.241456523779554</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-6.987510992988689</v>
+        <v>-6.874249220492118</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-7.668805880547374</v>
+        <v>-7.531739350625536</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-6.662634419335447</v>
+        <v>-6.500435781518696</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-7.12883813170999</v>
+        <v>-6.9672690078418</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 0.07399</t>
+          <t>X ≈ 0.07406</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.2639302077817689</v>
+        <v>0.22849607632687</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.844678792639478</v>
+        <v>4.795197186801957</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.452081254769404</v>
+        <v>4.403708000897417</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.615253526336041</v>
+        <v>5.900967473381101</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3.015691522970698</v>
+        <v>3.364642767408654</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>6.409957979098493</v>
+        <v>6.371496467281766</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.327084511717729</v>
+        <v>6.312636984871787</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.55083264363028</v>
+        <v>6.874915835593221</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.803005469997927</v>
+        <v>6.15588016244179</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.05547710739782</v>
+        <v>8.413484763948787</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>8.886734023983379</v>
+        <v>9.238369919755812</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>10.64671408296842</v>
+        <v>10.66813269685105</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>10.57420938161452</v>
+        <v>10.2759843539238</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>12.20613723774765</v>
+        <v>12.24016739137549</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 0.09406</t>
+          <t>X ≈ 0.09415</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.614330289914726</v>
+        <v>-1.888410970049868</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-3.5971944941004</v>
+        <v>-3.984886593911995</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.341400977978552</v>
+        <v>-2.862383269643743</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.9500107544444347</v>
+        <v>-1.719685364549221</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.2805672473973004</v>
+        <v>-0.4396668603592104</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.3242308475374927</v>
+        <v>-0.1638938965237173</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.250361919472297</v>
+        <v>0.7892499869480574</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.827603673777553</v>
+        <v>4.378506171915923</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.021213671482236</v>
+        <v>4.596018416564377</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.173632471158299</v>
+        <v>3.768848917853497</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>3.717557910671296</v>
+        <v>3.564906166403674</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3.753178173496849</v>
+        <v>3.764747931838194</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2.828273896684074</v>
+        <v>3.001298550267954</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>3.079118468651345</v>
+        <v>3.137879650606401</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.661902025923148</v>
+        <v>-1.709246384547015</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.609934343025479</v>
+        <v>-2.320519189232286</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.688896030708008</v>
+        <v>-1.73153057173252</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-2.217767010309096</v>
+        <v>-2.257264163451282</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.109977800789729</v>
+        <v>-1.437232308283242</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.472729610464242</v>
+        <v>-1.159682058304902</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.228638253279577</v>
+        <v>-0.8910173882549373</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.35483087987356</v>
+        <v>-2.014097360618372</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.72236599423168</v>
+        <v>-4.505686580859077</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-4.25430464472106</v>
+        <v>-4.167417381077868</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-4.789590259635638</v>
+        <v>-4.849247492688242</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-5.41618029521554</v>
+        <v>-5.44897549216553</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.208508363413756</v>
+        <v>-2.225712366097774</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.629073869569822</v>
+        <v>-1.647720135661359</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-4.097541692765908</v>
+        <v>-4.155395530178865</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-9.520717557218745</v>
+        <v>-10.02087796427936</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-11.38403373378197</v>
+        <v>-11.30569806140376</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-10.96497375935933</v>
+        <v>-10.58794144733758</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-10.91804559299839</v>
+        <v>-10.49209274875742</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-12.39102948818636</v>
+        <v>-11.99475267651588</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-14.24573318505215</v>
+        <v>-13.96579154818128</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-14.12947876875761</v>
+        <v>-13.97583497385507</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-12.42827688952818</v>
+        <v>-12.23765965399778</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-12.10362023486148</v>
+        <v>-11.87805628215005</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-12.31238106441689</v>
+        <v>-12.0821967296862</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-12.5772755418104</v>
+        <v>-12.31988798048692</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-13.29679167314156</v>
+        <v>-13.01090389521649</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-13.34670580975499</v>
+        <v>-13.05771702136674</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.174564734552817</v>
+        <v>0.4253318938212587</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.524206919793869</v>
+        <v>2.121600769385026</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.1372314766874396</v>
+        <v>0.5855631572593936</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.8715825938548392</v>
+        <v>-0.7527857920723022</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.394860458974676</v>
+        <v>-3.376673581432243</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.432019441466693</v>
+        <v>-3.580228995832137</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.530984796503894</v>
+        <v>-1.654130118170258</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.999480971566243</v>
+        <v>-2.119962878553601</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.061250578443641</v>
+        <v>-2.156935487690397</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.253181036869307</v>
+        <v>-1.325134929432458</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.790149462476194</v>
+        <v>-1.860401204783123</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.09725615601809068</v>
+        <v>-0.1466053283453874</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-3.506431067356132</v>
+        <v>-3.521895705240333</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-5.583987633371443</v>
+        <v>-5.59073163792695</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.1582848400155896</v>
+        <v>-0.3824522504188153</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.094679412575061</v>
+        <v>1.2258600261273</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.508049724887471</v>
+        <v>-2.713977252967382</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.161753108413734</v>
+        <v>-4.357142857142861</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.272320639452097</v>
+        <v>-3.427952281782645</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-2.979175501696872</v>
+        <v>-3.155166762963873</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.066579481947329</v>
+        <v>-3.215822852189177</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.893570605563667</v>
+        <v>-4.036265541650529</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.956491480339352</v>
+        <v>-4.073238150787411</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.019465054386686</v>
+        <v>-3.124017086212319</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-5.730819448999839</v>
+        <v>-5.810427037294517</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-4.625899312902284</v>
+        <v>-4.688430512695497</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-5.764921052100014</v>
+        <v>-5.792808297415426</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.443226252550048</v>
+        <v>-4.479933648165932</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>206</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.129746586384059</v>
+        <v>1.858820213947965</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.933614314051198</v>
+        <v>2.217390701607648</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.538824701508375</v>
+        <v>2.309089606496826</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.229218655325148</v>
+        <v>-0.473647711511795</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.857562860763075</v>
+        <v>3.406035186371234</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.702974598117791</v>
+        <v>2.222510025578515</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.617422489138718</v>
+        <v>2.161853936353054</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.7855014035224457</v>
+        <v>-0.2457263968459316</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.3631226564304839</v>
+        <v>0.2027378872213745</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.151129516168425</v>
+        <v>-2.562838266409251</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.872453840166251</v>
+        <v>-2.281541820741346</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-7.690360762819537</v>
+        <v>-7.077744015415512</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-4.71892772520409</v>
+        <v>-4.07484368955204</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.987367951405183</v>
+        <v>-3.340361934332904</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.384172042422122</v>
+        <v>0.968149044678178</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.215364300925785</v>
+        <v>-3.658506301347188</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.538908387076994</v>
+        <v>1.165147014685935</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.528837525072923</v>
+        <v>2.16459627329192</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.2772123252461043</v>
+        <v>-0.06378330244270103</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.286709037759486</v>
+        <v>1.948132651159028</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.347023814693351</v>
+        <v>4.061389605411733</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.305422213485457</v>
+        <v>0.9868611928545263</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.04441831038531063</v>
+        <v>-0.3544592423692805</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.545334697619943</v>
+        <v>2.299973046380956</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1913978243477459</v>
+        <v>-0.07808044463349972</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.219686001502865</v>
+        <v>-3.498174576833726</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.643119256214142</v>
+        <v>-3.893332503397552</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.811104141562538</v>
+        <v>-1.035591989208321</v>
       </c>
     </row>
     <row r="15">
@@ -1040,153 +1040,153 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-4.12273640617628</v>
+        <v>-4.140546607495622</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.503433680154288</v>
+        <v>3.515406742131077</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.9352268248993099</v>
+        <v>0.9477557103381145</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.02115470094288696</v>
+        <v>-0.009316770186345025</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.646183041761226</v>
+        <v>-1.585522432877383</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-3.212230911069199</v>
+        <v>-3.48664995753672</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-6.021994102923124</v>
+        <v>-6.264697351110009</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.227480242212607</v>
+        <v>-3.469660546275897</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.290753687002379</v>
+        <v>-3.506633155412693</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-6.323867682557029</v>
+        <v>-6.504374779706062</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.260032558075515</v>
+        <v>-3.447645662024698</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.229357411405822</v>
+        <v>-3.389478924659876</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.653734422205744</v>
+        <v>-3.784636851223631</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-5.594880286277125</v>
+        <v>-5.709505032686472</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 0.2546</t>
+          <t>X ≈ 0.2547</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.496655701582441</v>
+        <v>-2.510111824887055</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.576268885777104</v>
+        <v>-1.561643340422584</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.338336742909078</v>
+        <v>-1.322469936332233</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.475307518326041</v>
+        <v>-2.458408679927672</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.114082491364762</v>
+        <v>-1.048923643664402</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-6.516768899753032</v>
+        <v>-6.472340656491042</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-6.236295564113547</v>
+        <v>-6.532996745716503</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-4.173978050167293</v>
+        <v>-4.467183936479593</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-4.238621620641858</v>
+        <v>-4.504156545616461</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-5.727822196257122</v>
+        <v>-5.960896518836371</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-6.57250820503149</v>
+        <v>-6.797948358777589</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-7.181410968286592</v>
+        <v>-7.372693013817688</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-6.337200434409894</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-8.00690910532262</v>
+        <v>-8.151717470771281</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 0.2747</t>
+          <t>X ≈ 0.2748</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.27679386605498</v>
+        <v>3.259118944343932</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>11.92954717710202</v>
+        <v>11.93235211559819</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>8.325682162653621</v>
+        <v>8.333485922155354</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>7.171875262349765</v>
+        <v>7.181318681318601</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>10.48278816909338</v>
+        <v>10.53822338652052</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>9.496862338553626</v>
+        <v>9.528957623288321</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>4.279195976324672</v>
+        <v>4.340096405857587</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.905771223850522</v>
+        <v>2.592212363422966</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.2776153517049522</v>
+        <v>-0.00886280981639942</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.144709329965821</v>
+        <v>-3.396793954733866</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.352690002433413</v>
+        <v>-3.600934402269957</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.392725132475952</v>
+        <v>-1.619690741828151</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.404225536107013</v>
+        <v>1.190279536736227</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.2855201593600896</v>
+        <v>-0.4837525243253182</v>
       </c>
     </row>
     <row r="18">
@@ -1196,153 +1196,153 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.283837242363717</v>
+        <v>2.266958238807213</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.0336526031546498</v>
+        <v>0.04683847849219092</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.463730100436592</v>
+        <v>-5.442440911096398</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-5.334653745607262</v>
+        <v>-5.312556869881718</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-5.23554264739775</v>
+        <v>-5.164863335674397</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.663134147933697</v>
+        <v>-3.618192466536996</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.7150544573952686</v>
+        <v>0.7797501703523295</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.665118140490542</v>
+        <v>-1.596910615508719</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.345738436512974</v>
+        <v>-1.633883224645579</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-4.750526801453603</v>
+        <v>-5.005482506097579</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.405341035549263</v>
+        <v>-2.661852252996731</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>4.017619787766591</v>
+        <v>3.765741235960519</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.674074596315677</v>
+        <v>1.459755283918987</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>4.482883480011289</v>
+        <v>4.256570846571293</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.3149</t>
+          <t>X ≈ 0.315</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.2932416056232228</v>
+        <v>-0.3042294719458027</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-4.118856537973663</v>
+        <v>-4.093288910042794</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-5.993769435430067</v>
+        <v>-5.957615133651743</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.02999677729908967</v>
+        <v>0.05462184873962173</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.439870391709839</v>
+        <v>2.506549178375892</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>4.211203362596585</v>
+        <v>4.249922932488765</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.389908701094249</v>
+        <v>3.453972725616296</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3.658773483402044</v>
+        <v>3.723434082880004</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>7.280578318369926</v>
+        <v>7.362932061978547</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>6.150276496054488</v>
+        <v>5.803809363516507</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>5.211305155768351</v>
+        <v>4.864374798333358</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>8.197149601888228</v>
+        <v>7.863718006286483</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>4.820124881783734</v>
+        <v>4.527383609134425</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>5.066929064056879</v>
+        <v>4.776428471149792</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.3349</t>
+          <t>X ≈ 0.335</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-4.576484725620091</v>
+        <v>-4.550928151417601</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.065665309387512</v>
+        <v>-1.032064420246982</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.4526514649874471</v>
+        <v>-0.4053942452963142</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.378532216423203</v>
+        <v>-2.316326530612244</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.245467660330625</v>
+        <v>3.316873308027667</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>9.703087979758351</v>
+        <v>9.712107806438439</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>9.619101832524002</v>
+        <v>9.651451717212908</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>9.149675723628697</v>
+        <v>9.185618956829565</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>8.058366185310859</v>
+        <v>8.128238184427531</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>11.30181951742024</v>
+        <v>11.38604225667376</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>10.71945963114359</v>
+        <v>10.16149364587237</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>9.726684855637913</v>
+        <v>9.19925221997196</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>13.43051466897514</v>
+        <v>12.88572694646935</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>9.56482902587436</v>
+        <v>9.053139155423501</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.962082783256093</v>
+        <v>-1.843445158220248</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>7.335311595746127</v>
+        <v>7.240044423290492</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>16.42724179714806</v>
+        <v>16.17963976830913</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>11.06488659937201</v>
+        <v>10.9761904761904</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>16.03359727064553</v>
+        <v>15.82027466857189</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>6.782515187523863</v>
+        <v>6.759726854057476</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>5.333706610132019</v>
+        <v>5.365737431498687</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>10.32645354081929</v>
+        <v>10.23323800444867</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>10.24366832069411</v>
+        <v>10.19626539531196</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>18.92028182256045</v>
+        <v>18.70577014783024</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>24.14278082679736</v>
+        <v>23.83496303362747</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>23.69444253077511</v>
+        <v>22.55979643765902</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>24.65876626268214</v>
+        <v>23.49797184442854</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>23.03750237709595</v>
+        <v>21.08035003977732</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>8.439864134630149</v>
+        <v>8.359453392504236</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>12.70832757585774</v>
+        <v>12.57337775662392</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>12.27408879052105</v>
+        <v>12.17963976830912</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>22.67530070034014</v>
+        <v>22.45445134575569</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>11.87518425599517</v>
+        <v>11.82027466857188</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>9.231449723122587</v>
+        <v>9.194509462753125</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.264363064673837</v>
+        <v>3.336751924252312</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>7.211260258759481</v>
+        <v>7.218745250825485</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>5.66577681537462</v>
+        <v>5.732497279369767</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>6.272344543732622</v>
+        <v>6.357944060873706</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>7.519652358831408</v>
+        <v>7.603078975656452</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>9.043150847348713</v>
+        <v>9.110521075340195</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>9.512196838534329</v>
+        <v>8.715363148776369</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>9.761918170810688</v>
+        <v>8.964408010791651</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>72</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>7.228783902012246</v>
+        <v>7.212110397335238</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>8.394988066825768</v>
+        <v>8.406711089957163</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>9.389008249118149</v>
+        <v>9.40186199053143</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5.352594715058899</v>
+        <v>5.36507936507936</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>8.980840166653479</v>
+        <v>9.04249689079419</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>9.278282104369055</v>
+        <v>9.315282409613033</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>7.804659498207968</v>
+        <v>7.865737431498765</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4.559698321648533</v>
+        <v>4.622126893337487</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>5.887587324355202</v>
+        <v>5.974043173089662</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>7.815239917105046</v>
+        <v>7.927992370052451</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>11.77715325945414</v>
+        <v>11.89051858918303</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>17.36709197235504</v>
+        <v>17.5042408821034</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>16.94683736141022</v>
+        <v>17.10908295553966</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>11.64100313813096</v>
+        <v>11.80257226199947</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>82</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.384610460277869</v>
+        <v>2.367936955600861</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.665987542930395</v>
+        <v>-1.654264519799</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.597680335838859</v>
+        <v>1.61053407725214</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.5084212733245224</v>
+        <v>0.5209059233449835</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.02999994174776077</v>
+        <v>0.03165678239295033</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5.145490776455773</v>
+        <v>5.182491081699752</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8.719293644549289</v>
+        <v>8.780371577840086</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>9.471622440889867</v>
+        <v>9.534051012578821</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>14.2886713351953</v>
+        <v>14.37512718392976</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>12.21903395504543</v>
+        <v>12.33178640799284</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>10.79476843560593</v>
+        <v>10.90813376533482</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.512078422219687</v>
+        <v>3.649227331968042</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>6.750360396640573</v>
+        <v>6.912605990770004</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.56105733867296</v>
+        <v>4.72262646254147</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>71</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.84458984880407</v>
+        <v>3.827916344127061</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.641466940065207</v>
+        <v>3.653189963196603</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.063499641919279</v>
+        <v>6.07635338333256</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>6.193752774526779</v>
+        <v>6.20623742454724</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>8.472232967905356</v>
+        <v>8.533889692046067</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>10.1781256098464</v>
+        <v>10.21512591509038</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>10.09339189257413</v>
+        <v>10.15446982586492</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>11.03465919801798</v>
+        <v>11.09708776970694</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>6.748307199159576</v>
+        <v>6.834763047894036</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>8.715083422582367</v>
+        <v>8.827835875529772</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>9.91878080249009</v>
+        <v>10.03214613221898</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>11.36161466406091</v>
+        <v>11.49876357380926</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>13.75826146156671</v>
+        <v>13.92050705569614</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>15.41643349806839</v>
+        <v>15.5780026219369</v>
       </c>
     </row>
     <row r="26">
@@ -1615,98 +1615,98 @@
         <v>67</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>10.19312884396913</v>
+        <v>10.17645533929213</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.103943290706368</v>
+        <v>4.115666313837764</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.201611897542648</v>
+        <v>5.214465638955929</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>14.28708891074708</v>
+        <v>14.29957356076754</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.7934438150779</v>
+        <v>4.855100539218611</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>8.075960379659236</v>
+        <v>8.112960684903214</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>7.991226662386957</v>
+        <v>8.052304595677754</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>9.016580577038276</v>
+        <v>9.079009148727231</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>10.44811800428887</v>
+        <v>10.53457385302332</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>9.59799281926098</v>
+        <v>9.710745272208385</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>7.900702181510567</v>
+        <v>8.01406751123946</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.457473398557482</v>
+        <v>3.594622308305837</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.529756101045379</v>
+        <v>4.69200169517481</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.272014746754465</v>
+        <v>6.433583870622975</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.4755</t>
+          <t>X ≈ 0.4756</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>36</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>11.39545056867887</v>
+        <v>11.37877706400187</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>7.006099177936839</v>
+        <v>7.017822201068235</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>12.16678602689583</v>
+        <v>12.17963976830912</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.96370582617017</v>
+        <v>3.976190476190631</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>6.203062388875701</v>
+        <v>6.264719113016412</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.722726548813462</v>
+        <v>3.75972685405744</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.917562724014331</v>
+        <v>-1.856484790723535</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.948587210537504</v>
+        <v>6.011015782226458</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>11.44314287991072</v>
+        <v>11.52959872864518</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>7.815239917104968</v>
+        <v>7.927992370052372</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.054931037231839</v>
+        <v>2.168296366960732</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>13.20042530568834</v>
+        <v>13.3375742154367</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>12.78017069474352</v>
+        <v>12.94241628887296</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>13.02989202701984</v>
+        <v>13.19146115088835</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>30</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>10.83989501312341</v>
+        <v>10.8232215084464</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.89498806682581</v>
+        <v>5.906711089957206</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>8.833452693562506</v>
+        <v>8.846306434975787</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.630372492836585</v>
+        <v>5.642857142857046</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>5.091951277764508</v>
+        <v>5.153608001905219</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.389393215480268</v>
+        <v>5.426393520724247</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.971326164874554</v>
+        <v>2.032404098165351</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.504142766093054</v>
+        <v>1.566571337782008</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.890190453422477</v>
+        <v>-1.803734604688017</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>7.259684361549546</v>
+        <v>7.37243681449695</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.945068962768083</v>
+        <v>-2.83170363303919</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-9.577352472089274</v>
+        <v>-9.440203562340919</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.330940416367454</v>
+        <v>-3.168694822238024</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>6.918780915908783</v>
+        <v>7.080350039777294</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>32</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-13.48001193317423</v>
+        <v>-13.46828891004284</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-7.624880639770822</v>
+        <v>-7.612026898357541</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-16.86962750716332</v>
+        <v>-16.85714285714286</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-14.28304872223549</v>
+        <v>-14.22139199809478</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-20.23560678451983</v>
+        <v>-20.19860647927585</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-10.94534050179211</v>
+        <v>-10.88426256850131</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-8.287523900573611</v>
+        <v>-8.225095328884656</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.151476213244045</v>
+        <v>4.237932061978505</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.948648971783882</v>
+        <v>-2.835896518836478</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.096597703898581</v>
+        <v>3.209963033627474</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.4142737497009321</v>
+        <v>-0.2520281555715016</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>2.960447582575355</v>
+        <v>3.122016706443866</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>18</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>25.28433945756781</v>
+        <v>25.2676659528908</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>7.006099177936882</v>
+        <v>7.017822201068277</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>23.27789713800703</v>
+        <v>23.29075087942032</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>23.40815027061446</v>
+        <v>23.42063492063492</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>11.75861794443117</v>
+        <v>11.82027466857188</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>6.500504326591198</v>
+        <v>6.537504631835176</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>11.97132616487455</v>
+        <v>12.03240409816534</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>11.50414276609305</v>
+        <v>11.566571337782</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.887587324355202</v>
+        <v>5.974043173089662</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>16.14857325043837</v>
+        <v>16.26132570338578</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>15.9438199261208</v>
+        <v>16.05718525584969</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>15.97820308346631</v>
+        <v>16.11535199321467</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>21.1135040280769</v>
+        <v>21.27574962220633</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>21.36322536035318</v>
+        <v>21.52479448422169</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>16</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-27.49343832020998</v>
+        <v>-27.51011182488698</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-10.35501193317423</v>
+        <v>-10.34328891004284</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-16.99988063977091</v>
+        <v>-16.98702689835763</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-10.61962750716332</v>
+        <v>-10.60714285714286</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-17.40804872223549</v>
+        <v>-17.34639199809478</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-4.610606784519916</v>
+        <v>-4.573606479275938</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.087476099426475</v>
+        <v>1.149904671115429</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1.026476213244173</v>
+        <v>1.112932061978633</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1763510282162457</v>
+        <v>0.2891034811636501</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.02840229610133349</v>
+        <v>0.08496303362755953</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-6.244019138756073</v>
+        <v>-6.106870229007718</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-19.16427374970089</v>
+        <v>-19.00202815557146</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-25.16455241742469</v>
+        <v>-25.00298329355618</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>13</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-6.339592166363822</v>
+        <v>-6.356265671040831</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-15.64347347163577</v>
+        <v>-15.63175044850437</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.038580898690718</v>
+        <v>7.051434640103999</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.5234736610093691</v>
+        <v>-0.5109890109889079</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.630412816226048</v>
+        <v>6.692069540366759</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.927854753941922</v>
+        <v>6.964855059185901</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-8.541494347945957</v>
+        <v>-8.48041641465516</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-9.008677746727564</v>
+        <v>-8.946249175038609</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-9.069677632909865</v>
+        <v>-8.983221784175406</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-2.227495125630107</v>
+        <v>-2.114742672682702</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.260059242359901</v>
+        <v>5.373424572088794</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.294442399705552</v>
+        <v>5.431591309453907</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>4.874187788760651</v>
+        <v>5.036433382890081</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-17.95301395588598</v>
+        <v>-17.79144483201747</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>24</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>8.394988066825732</v>
+        <v>8.406711089957128</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>12.16678602689588</v>
+        <v>12.17963976830916</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>16.46370582616992</v>
+        <v>16.47619047619038</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>7.591951277764508</v>
+        <v>7.653608001905219</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.4439401178532236</v>
+        <v>-0.4069398126092452</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-13.49585723390694</v>
+        <v>-13.43342866221798</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-13.55685712008924</v>
+        <v>-13.47040127135478</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-10.24031563845048</v>
+        <v>-10.12756318550307</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-6.278402296101362</v>
+        <v>-6.165036966372469</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-10.41068580542262</v>
+        <v>-10.27353689567427</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-14.99760708303422</v>
+        <v>-14.83536148890479</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-18.9145524174246</v>
+        <v>-18.75298329355609</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>21</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>14.17322834645668</v>
+        <v>14.15655484177967</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>22.08546425730199</v>
+        <v>22.09718728043338</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.404881264991054</v>
+        <v>7.417735006404335</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.535134397598618</v>
+        <v>7.547619047619079</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>2.234808420621647</v>
+        <v>2.296465144762358</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.532250358337272</v>
+        <v>2.569250663581251</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>7.209421402969795</v>
+        <v>7.270499336260592</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.980333242283564</v>
+        <v>2.042761813972518</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>6.681238118005993</v>
+        <v>6.767693966740453</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-3.692696590831488</v>
+        <v>-3.579944137884084</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.8644548467556845</v>
+        <v>0.9778201764845775</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-3.863066757803637</v>
+        <v>-3.725917848055282</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-13.80713089255804</v>
+        <v>-13.6448852984286</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-8.795504798376989</v>
+        <v>-8.633935674508479</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that BB Width-20 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that BB Width-20 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2210,209 +2210,209 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 0.04388</t>
+          <t>X &gt; 0.04396</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4075</v>
+        <v>4087</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.02279252764638073</v>
+        <v>-0.02230694683819934</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1156878466153373</v>
+        <v>0.1150545883714074</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.02117285709827854</v>
+        <v>-0.02143392617598749</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07345694816103077</v>
+        <v>0.07292792635725931</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.08705411811710206</v>
+        <v>0.08524862690521928</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.006096619839702555</v>
+        <v>0.005148099478724077</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.08975500448686802</v>
+        <v>-0.09102856752427613</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.1269933933449821</v>
+        <v>-0.1281920794343705</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.1499943749912021</v>
+        <v>-0.1517306946196939</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1530802049292248</v>
+        <v>-0.1554699727596827</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.1969898390146056</v>
+        <v>-0.1992667952233802</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.2224346403503006</v>
+        <v>-0.2252365777481558</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.2118694317421088</v>
+        <v>-0.215335396275961</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.2427732763203068</v>
+        <v>-0.2461323026091833</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 0.06395</t>
+          <t>X &gt; 0.06403</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3935</v>
+        <v>3947</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.08715665860916744</v>
+        <v>-0.08586940064455462</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.03737468957722712</v>
+        <v>0.0365418553019552</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.03966776597457056</v>
+        <v>-0.04033665075774451</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1043902368163998</v>
+        <v>0.1033069785912772</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.06152531427566998</v>
+        <v>0.0575513790538551</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.06857150612180618</v>
+        <v>0.06609010732339016</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.04844437897907738</v>
+        <v>0.04454370362817173</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.001140144085098882</v>
+        <v>-0.002700944872515265</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.00490260918317631</v>
+        <v>-0.0004282619080910877</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.03196158927227088</v>
+        <v>0.024929854233676</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.04460430623479539</v>
+        <v>0.03749467919709559</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.04249343426916141</v>
+        <v>0.03392490900198908</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.01763681940479955</v>
+        <v>0.007596971074939063</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.002220136577932408</v>
+        <v>-0.007733736930802593</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 0.08403</t>
+          <t>X &gt; 0.0841</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3645</v>
+        <v>3655</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.1150894957157149</v>
+        <v>-0.1109842349196981</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.345099436592335</v>
+        <v>-0.3436297881448311</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.3970360008211458</v>
+        <v>-0.3953738705343</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3340597917050445</v>
+        <v>-0.3598713701032921</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.173511229077306</v>
+        <v>-0.2066540068284013</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.4359558127158394</v>
+        <v>-0.4376523433217159</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.4510907756146665</v>
+        <v>-0.456217784230418</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.5199602193903701</v>
+        <v>-0.5521576069507645</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.4564004990846726</v>
+        <v>-0.4922591948520463</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.6063976700573335</v>
+        <v>-0.6452365024385074</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.658884752241768</v>
+        <v>-0.6975684043167618</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.8011894156959372</v>
+        <v>-0.8156479156360206</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.8222550991249165</v>
+        <v>-0.8127502562279076</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.9687362308676768</v>
+        <v>-0.9862254276190114</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 0.1041</t>
+          <t>X &gt; 0.1042</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3250</v>
+        <v>3261</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.06712592388693395</v>
+        <v>0.1037677226519946</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.05015519347403341</v>
+        <v>0.09631353644034135</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1607208728281648</v>
+        <v>-0.0973052709485458</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.2591980593105632</v>
+        <v>-0.1955761496765263</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2286992285257625</v>
+        <v>-0.178500966567384</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.5283477298850912</v>
+        <v>-0.4707283408802567</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.657882718556003</v>
+        <v>-0.6066974842746689</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.169894907944624</v>
+        <v>-1.147889446531714</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.122141298276645</v>
+        <v>-1.107034226712841</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.187355179528161</v>
+        <v>-1.178554397438518</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.190790860503512</v>
+        <v>-1.212568398448575</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.354720245767062</v>
+        <v>-1.369059741427137</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.265934777077085</v>
+        <v>-1.273570627205935</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.460706263578452</v>
+        <v>-1.484507365926532</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2947</v>
+        <v>2957</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.2448983937859737</v>
+        <v>0.2901580806460728</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.3236560857574844</v>
+        <v>0.3447806140881156</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.003599368641680201</v>
+        <v>0.07070436430282712</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.05782500462697016</v>
+        <v>0.01637960148597983</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1380893176346802</v>
+        <v>-0.04909470079748246</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.4312497625232083</v>
+        <v>-0.399899145717221</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.5991996757934572</v>
+        <v>-0.5774674366554677</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.048064029256309</v>
+        <v>-1.058837297095678</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.7519790713087602</v>
+        <v>-0.7576293177982549</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.8720224045185034</v>
+        <v>-0.8712786629013678</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.8207751774573495</v>
+        <v>-0.8386926985335066</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.9371354493697552</v>
+        <v>-0.9496162553857204</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.169022732061812</v>
+        <v>-1.17568388773244</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.443395308500271</v>
+        <v>-1.467727967211822</v>
       </c>
     </row>
     <row r="11">
@@ -2474,153 +2474,153 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2608</v>
+        <v>2619</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.8093490031958979</v>
+        <v>0.8638874126273066</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.603273672018588</v>
+        <v>1.682540293159605</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.475682552287218</v>
+        <v>1.538907502862905</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.359937045930643</v>
+        <v>1.384940317218074</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.263139661409909</v>
+        <v>1.298646169844154</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.123338169608616</v>
+        <v>1.096496613507654</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.174640377748993</v>
+        <v>1.150388061510142</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.6523192516834655</v>
+        <v>0.6081902763081644</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.7657605607373981</v>
+        <v>0.7239477168086381</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.5879130496556755</v>
+        <v>0.5492218469520296</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.6729573362233623</v>
+        <v>0.6123589862811585</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.5759042328915172</v>
+        <v>0.5177956740087808</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.4074012215524618</v>
+        <v>0.3517328219008604</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.1038524905508567</v>
+        <v>0.02803999777647448</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 0.1643</t>
+          <t>X &gt; 0.1644</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2307</v>
+        <v>2317</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.9377226638211056</v>
+        <v>0.921049159144097</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.613589706877555</v>
+        <v>1.62531273000895</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.650313576888657</v>
+        <v>1.663167318301937</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.651088936513844</v>
+        <v>1.663573586534305</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.870880466020118</v>
+        <v>1.908031825815449</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.71768695198125</v>
+        <v>1.706065510365924</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.527649990861306</v>
+        <v>1.515931648158166</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.9983061902175692</v>
+        <v>0.9637803724532858</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.134607701133362</v>
+        <v>1.099444793959563</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.8281251519721167</v>
+        <v>0.7935273050737948</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.9943249766258546</v>
+        <v>0.9346609188238517</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.663733134955578</v>
+        <v>0.6043943372418283</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.9180486073181768</v>
+        <v>0.8566252755895292</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.8459590693547625</v>
+        <v>0.7603960763187487</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 0.1844</t>
+          <t>X &gt; 0.1845</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2028</v>
+        <v>2035</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.088504761242426</v>
+        <v>1.101681786906632</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.68497825328307</v>
+        <v>1.68066686391294</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.222396102133011</v>
+        <v>2.269729858399216</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.450784661629612</v>
+        <v>2.497893997893996</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.578451032305495</v>
+        <v>2.64746549576271</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.363852940431059</v>
+        <v>2.379710474041104</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.159696353244748</v>
+        <v>2.171634237395494</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.67130107484428</v>
+        <v>1.656661427872102</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.835010399176205</v>
+        <v>1.816249015295504</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.357453390420886</v>
+        <v>1.336400778460863</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.919529757074351</v>
+        <v>1.869361068025512</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.391448841539578</v>
+        <v>1.337847215709807</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.837451237977774</v>
+        <v>1.77807012452682</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.57361326304877</v>
+        <v>1.48657444600164</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1822</v>
+        <v>1829</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.08384185455791</v>
+        <v>1.016405397638984</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.656866821604574</v>
+        <v>1.620215737305443</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.29968244051318</v>
+        <v>2.26529677578133</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.86685528912286</v>
+        <v>2.832578301960474</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.546893932051788</v>
+        <v>2.56202790349078</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.438573543349023</v>
+        <v>2.397415937345258</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.221007229208439</v>
+        <v>2.17273579125812</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.949073473605822</v>
+        <v>1.870927087736455</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.083536968580702</v>
+        <v>1.997978535461321</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.867205354612658</v>
+        <v>1.77557149647248</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.461323731295849</v>
+        <v>2.336876647624187</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.418261562998403</v>
+        <v>2.285694013747971</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.578732284308984</v>
+        <v>2.437282943389718</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.202352083124246</v>
+        <v>2.030231577958396</v>
       </c>
     </row>
     <row r="15">
@@ -2682,153 +2682,153 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1590</v>
+        <v>1599</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.040020091297222</v>
+        <v>1.023346586620214</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2.367783564011511</v>
+        <v>2.379506587142906</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.410688465920231</v>
+        <v>2.423542207333512</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.916176120103721</v>
+        <v>2.928660770124182</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.878067600466196</v>
+        <v>2.939724324606907</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.460732389447628</v>
+        <v>2.462040800273861</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.910796004156545</v>
+        <v>1.901072015613757</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.042989883887536</v>
+        <v>1.998091037594399</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.394031072178258</v>
+        <v>2.336352950033586</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.768258180035488</v>
+        <v>1.700141630006591</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>2.79253304602036</v>
+        <v>2.684243834127791</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>3.240905484359587</v>
+        <v>3.117645093068667</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>3.486574773240655</v>
+        <v>3.347878035798146</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.642051356160302</v>
+        <v>2.471219333085564</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 0.2446</t>
+          <t>X &gt; 0.2447</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1407</v>
+        <v>1415</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.711508676256457</v>
+        <v>1.694835171579449</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.220076406048385</v>
+        <v>2.23179942917978</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.602592858462394</v>
+        <v>2.615446599875675</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.298217015804873</v>
+        <v>3.310701665825334</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.466509581651437</v>
+        <v>3.528166305792148</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.198580494632111</v>
+        <v>3.235580799876089</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.942566146015523</v>
+        <v>2.962910576375009</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.728488130565815</v>
+        <v>2.709091950267286</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.133416723159101</v>
+        <v>3.096147609681722</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.820752162163721</v>
+        <v>2.76701867550986</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.57975373226737</v>
+        <v>3.481606143168108</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>4.082453536900509</v>
+        <v>3.963801149084247</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>4.415271704844571</v>
+        <v>4.27535700343914</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.713379352298219</v>
+        <v>3.535002572168288</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 0.2647</t>
+          <t>X &gt; 0.2648</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.240054122113023</v>
+        <v>2.223380617436014</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.696897374701663</v>
+        <v>2.708620397833059</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.097573616394648</v>
+        <v>3.110427357807929</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>4.023371697291729</v>
+        <v>4.03585634731219</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.04183194602227</v>
+        <v>4.103488670162982</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.418828378566886</v>
+        <v>4.455828683810864</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>4.095431176807729</v>
+        <v>4.156509110098526</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.59543788286588</v>
+        <v>3.611121854886228</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.059344739140506</v>
+        <v>4.051476214723174</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.894453101581384</v>
+        <v>3.864083592539856</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>4.854877831592113</v>
+        <v>4.773706072609173</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>5.497194918752001</v>
+        <v>5.388754273776776</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>5.765782205534919</v>
+        <v>5.630032305844615</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>5.185447582575399</v>
+        <v>5.003977724741439</v>
       </c>
     </row>
     <row r="18">
@@ -2838,49 +2838,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.093301007673759</v>
+        <v>2.07662750299675</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.389992608151836</v>
+        <v>1.401715631283231</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.357521721718726</v>
+        <v>2.370375463132007</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.577693110457027</v>
+        <v>3.590177760477488</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.130098416729091</v>
+        <v>3.191755140869802</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.700019918477437</v>
+        <v>3.737020223721416</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>4.069418807926333</v>
+        <v>4.130496741217129</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.693061930489066</v>
+        <v>3.75549050217802</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>4.594658031425901</v>
+        <v>4.626783106483551</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>4.890864222028711</v>
+        <v>4.892872781799348</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>6.016679671111696</v>
+        <v>5.960303633082511</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>6.472480405455499</v>
+        <v>6.381776455824337</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>6.383171505773568</v>
+        <v>6.259098093293211</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>5.959876806319684</v>
+        <v>5.781530784554711</v>
       </c>
     </row>
     <row r="19">
@@ -2890,101 +2890,101 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.061646425552738</v>
+        <v>2.044972920875729</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.615327049876612</v>
+        <v>1.627050073008007</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.656899021246119</v>
+        <v>3.6697527626594</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5.058338594531598</v>
+        <v>5.070823244552059</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4.519917379459429</v>
+        <v>4.58157410360014</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>4.923291520564909</v>
+        <v>4.960291825808888</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>4.62669339651297</v>
+        <v>4.687771329803766</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4.583238811290791</v>
+        <v>4.645667382979745</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>5.581560959006801</v>
+        <v>5.66801680774126</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>6.492628864907566</v>
+        <v>6.539103481163565</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>7.415865219822145</v>
+        <v>7.394285067525779</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>6.880316674208942</v>
+        <v>6.816858584551689</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>7.165513484341666</v>
+        <v>7.057293878326846</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>6.205255889284665</v>
+        <v>6.035152299664247</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.3249</t>
+          <t>X &gt; 0.325</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.457056729294976</v>
+        <v>2.440383224617968</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.578156383657443</v>
+        <v>2.589879406788839</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5.277347083001452</v>
+        <v>5.290200824414732</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5.902649720559445</v>
+        <v>5.915134370579906</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>4.869179000536782</v>
+        <v>4.930835724677493</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.042858562014821</v>
+        <v>5.0798588672588</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4.834362468504914</v>
+        <v>4.89544040179571</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>4.738466198436285</v>
+        <v>4.80089477012524</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>5.296278193442106</v>
+        <v>5.382734042176565</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>6.550113404453782</v>
+        <v>6.662865857401187</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>7.786033887293868</v>
+        <v>7.820111548478963</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>6.659206667695628</v>
+        <v>6.640654523467617</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>7.559328734771164</v>
+        <v>7.483120359280029</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>6.396392856207243</v>
+        <v>6.247016706443908</v>
       </c>
     </row>
     <row r="21">
@@ -2994,49 +2994,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3.422054637536505</v>
+        <v>3.405381132859496</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.078086658375064</v>
+        <v>3.089809681506459</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>6.063499641919314</v>
+        <v>6.076353383332595</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>7.038823197062023</v>
+        <v>7.051307847082484</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>5.091951277764508</v>
+        <v>5.153608001905219</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>4.403477722522425</v>
+        <v>4.440478027766403</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.17789893482761</v>
+        <v>4.238976868118407</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>4.13325074731371</v>
+        <v>4.195679319002664</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>4.917321283666624</v>
+        <v>5.003777132401083</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>5.898182014131649</v>
+        <v>6.010934467079053</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>7.383569534884501</v>
+        <v>7.496934864613394</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>6.238350395799728</v>
+        <v>6.287495968175463</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>6.753805346344308</v>
+        <v>6.737408464146853</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>5.961685206337776</v>
+        <v>5.859692762781933</v>
       </c>
     </row>
     <row r="22">
@@ -3046,49 +3046,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>4.041994750656158</v>
+        <v>4.02532124597915</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.587901452652538</v>
+        <v>2.599624475783934</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>4.870198100386659</v>
+        <v>4.88305184179994</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>6.575254382600455</v>
+        <v>6.587739032620917</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.832108758079464</v>
+        <v>3.893765482220175</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>4.129550695795125</v>
+        <v>4.166551001039103</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4.044816978522846</v>
+        <v>4.105894911813643</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.420153264780723</v>
+        <v>3.482581836469677</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.304035268362192</v>
+        <v>4.390491117096651</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>4.398791973098049</v>
+        <v>4.511544426045454</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>5.453881168465507</v>
+        <v>5.5672464981944</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>4.228421806125901</v>
+        <v>4.365570715874256</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>4.692193127270713</v>
+        <v>4.757814364113578</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.995542219799376</v>
+        <v>4.06197733636516</v>
       </c>
     </row>
     <row r="23">
@@ -3101,98 +3101,98 @@
         <v>566</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.513628817599212</v>
+        <v>3.496955312922204</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.372019868945905</v>
+        <v>1.383742892077301</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.980684731253916</v>
+        <v>3.993538472667197</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.640973199550459</v>
+        <v>4.65345784957092</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.865802867870514</v>
+        <v>2.927459592011225</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>3.516601696045541</v>
+        <v>3.553602001289519</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4.138581759691988</v>
+        <v>4.199659692982785</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.964684579991761</v>
+        <v>3.027113151680716</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.140433810417235</v>
+        <v>4.226889659151695</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>4.17370085153771</v>
+        <v>4.286453304485114</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.205696643827913</v>
+        <v>5.319061973556806</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.649973794106209</v>
+        <v>3.787122703854564</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4.11311140930971</v>
+        <v>4.27535700343914</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.302762070207912</v>
+        <v>3.464331194076422</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.4052</t>
+          <t>X &gt; 0.4053</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>494</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.972148724324441</v>
+        <v>2.955475219647433</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.3484293623723218</v>
+        <v>0.3601523855037172</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.192427052536864</v>
+        <v>3.205280793950145</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.537255083929793</v>
+        <v>4.549739733950254</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.974542370881913</v>
+        <v>2.036199095022624</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.676842608192722</v>
+        <v>2.7138429134367</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.604254639908291</v>
+        <v>3.665332573199088</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.732212941531657</v>
+        <v>2.794641513220611</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.885787954134777</v>
+        <v>3.972243802869237</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.642950218499564</v>
+        <v>3.755702671446969</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.247913493372266</v>
+        <v>4.361278823101159</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.650717703349279</v>
+        <v>1.787866613097634</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.242608841392226</v>
+        <v>2.404854435521656</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.087471874073373</v>
+        <v>2.249040997941883</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>412</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.089085951634679</v>
+        <v>3.072412446957671</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.7493569988645987</v>
+        <v>0.7610800219959941</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.509828098093251</v>
+        <v>3.522681839506532</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.33911035691434</v>
+        <v>5.351595006934801</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.373504675822758</v>
+        <v>2.435161399963469</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.185509720334537</v>
+        <v>2.222510025578515</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.58621289626614</v>
+        <v>2.647290829556937</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.390874157678816</v>
+        <v>1.45330272936777</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.815311164700397</v>
+        <v>1.901767013434856</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.936059766080234</v>
+        <v>2.048812219027639</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.944898674772361</v>
+        <v>3.058264004501254</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.280252705904203</v>
+        <v>1.417401615652558</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.345434988163184</v>
+        <v>1.507680582292615</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.595156320439472</v>
+        <v>1.756725444307982</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>341</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.931781621138995</v>
+        <v>2.915108116461987</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.1471874803155018</v>
+        <v>0.1589105034468972</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.978125225331823</v>
+        <v>2.990978966745104</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.161164281692983</v>
+        <v>5.173648931713444</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.103681483043097</v>
+        <v>1.165338207183808</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.5213580248643268</v>
+        <v>0.5583583301083053</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.023134571521666</v>
+        <v>1.084212504812463</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.6170693551190709</v>
+        <v>-0.5546407834301164</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.7882064185226767</v>
+        <v>0.8746622672571363</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.5245914974243746</v>
+        <v>0.637343950371779</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.492858700966032</v>
+        <v>1.606224030694925</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.8187991974070172</v>
+        <v>-0.6816502876586625</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.239053808351919</v>
+        <v>-1.076808214222488</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.282587608040444</v>
+        <v>-1.121018484171934</v>
       </c>
     </row>
     <row r="27">
@@ -3309,98 +3309,98 @@
         <v>274</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.156196716286374</v>
+        <v>1.139523211609365</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.8203404003275168</v>
+        <v>-0.8086173771961214</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.434425929572242</v>
+        <v>2.447279670985523</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.929642565829383</v>
+        <v>2.942127215849844</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.2014403288594053</v>
+        <v>0.2630970530001164</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.325935251673116</v>
+        <v>-1.288934946429137</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.6807419616461274</v>
+        <v>-0.6196640283553307</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-2.972742878675803</v>
+        <v>-2.910314306986848</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.573888750259563</v>
+        <v>-1.487432901525104</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.694086927988224</v>
+        <v>-1.581334475040819</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.07402273405762827</v>
+        <v>0.03934259567126475</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.864457094960372</v>
+        <v>-1.727308185212017</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.649675209554907</v>
+        <v>-2.487429615425476</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-3.129880884577886</v>
+        <v>-2.968311760709376</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.4855</t>
+          <t>X &gt; 0.4856</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>238</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.3925979840755147</v>
+        <v>-0.4092714887525233</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.004171597039772</v>
+        <v>-1.992448573908376</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.9623042341787595</v>
+        <v>0.9751579755920403</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.773229635693816</v>
+        <v>2.785714285714278</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.706368049966585</v>
+        <v>-0.6447113258258739</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-2.089598381158481</v>
+        <v>-2.052598075914503</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.4936598295232031</v>
+        <v>-0.4325818962324064</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-4.322187766119832</v>
+        <v>-4.259759194430877</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-3.542851517848341</v>
+        <v>-3.456395669113881</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-3.132472501195601</v>
+        <v>-3.019720048248196</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.3960493549249477</v>
+        <v>-0.2826840251960547</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-4.143178802621527</v>
+        <v>-4.006029892873173</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-4.983601480793318</v>
+        <v>-4.821355886663888</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-5.574216282970823</v>
+        <v>-5.412647159102313</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>208</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.012669089440749</v>
+        <v>-2.029342594117757</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-3.143473471635772</v>
+        <v>-3.131750448504377</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.1729575628477491</v>
+        <v>-0.1601038214344683</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.361141723605904</v>
+        <v>2.373626373626365</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.542664106850879</v>
+        <v>-1.481007382710168</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-3.168299092212145</v>
+        <v>-3.131298786968166</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.8491866556382632</v>
+        <v>-0.7881087223474665</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-5.100095328884656</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3.781216094448226</v>
+        <v>-3.694760245713766</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-4.631341279476153</v>
+        <v>-4.518588826528749</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.02840229610141876</v>
+        <v>0.08496303362747426</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-3.359403754140601</v>
+        <v>-3.222254844392246</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-5.221966057393203</v>
+        <v>-5.059720463263773</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-7.376090878963069</v>
+        <v>-7.214521755094559</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>176</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.925256502028155</v>
+        <v>-1.941930006705164</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.264102842265139</v>
+        <v>-1.252379819133743</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.181937542047358</v>
+        <v>1.194791283460638</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.857645220109404</v>
+        <v>5.870129870129865</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.7737694595826881</v>
+        <v>0.8354261837233992</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.06515223906529144</v>
+        <v>-0.02815193382131298</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.9864776800260699</v>
+        <v>1.047555613316867</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-4.59434208239179</v>
+        <v>-4.531913510702836</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-4.937285335420206</v>
+        <v>-4.824532882472802</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.5965841142832389</v>
+        <v>-0.4832187845543459</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.834928229665081</v>
+        <v>-2.697779319916727</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-6.096091931519069</v>
+        <v>-5.933846337389639</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-9.255461508333688</v>
+        <v>-9.093892384465178</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>158</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-5.025083889830228</v>
+        <v>-5.041757394507236</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-2.206277755959043</v>
+        <v>-2.194554732827648</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.335323677745514</v>
+        <v>-1.322469936332233</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.858220594102498</v>
+        <v>3.870705244122959</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.47766897540005</v>
+        <v>-0.4160122512593389</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.8131384300894524</v>
+        <v>-0.776138124845474</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.2649607549566682</v>
+        <v>-0.2038828216658715</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-6.428346685383737</v>
+        <v>-6.365918113694782</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-6.489346571566038</v>
+        <v>-6.402890722831579</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-7.339471756593966</v>
+        <v>-7.226719303646561</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.48093394167104</v>
+        <v>-2.367568611942147</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-4.978196353945869</v>
+        <v>-4.841047444197514</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-9.195919319321142</v>
+        <v>-9.033673725191711</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-12.74366634147523</v>
+        <v>-12.58209721760672</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>142</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.288110524723528</v>
+        <v>-1.276387501592133</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.4296968250179134</v>
+        <v>0.4425505664311942</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5.489527422414142</v>
+        <v>5.502012072434603</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.429979446778596</v>
+        <v>1.491636170919307</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.3852546718437679</v>
+        <v>-0.3482543665997895</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.2342369629966257</v>
+        <v>0.2953148962874224</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-7.275199956911642</v>
+        <v>-7.212771385222688</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-7.336199843093944</v>
+        <v>-7.249743994359484</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-8.186325028121871</v>
+        <v>-8.073572575174467</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-2.757275535538042</v>
+        <v>-2.643910205809149</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-4.835568434530636</v>
+        <v>-4.698419524782281</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-8.072724453926241</v>
+        <v>-7.910478859796811</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-11.34412988221333</v>
+        <v>-11.18256075834482</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>129</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.105841420985172</v>
+        <v>-2.12251492566218</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1585539582986328</v>
+        <v>0.1702769814300282</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2363147482979571</v>
+        <v>-0.2234610068846763</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.095488771906439</v>
+        <v>6.1079734219269</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.9059047661366009</v>
+        <v>0.967561490277312</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.12223469149658</v>
+        <v>-1.085234386252601</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1.118612986579983</v>
+        <v>1.179690919870779</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-7.100508396697641</v>
+        <v>-7.038079825008687</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-7.161508282879943</v>
+        <v>-7.075052434145483</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-8.786827266357484</v>
+        <v>-8.67407481341008</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-3.565224001527767</v>
+        <v>-3.451858671798874</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-5.856422239531184</v>
+        <v>-5.71927332978283</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-9.377452044274534</v>
+        <v>-9.215206450145104</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-10.67811830889747</v>
+        <v>-10.51654918502896</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>105</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.017247844019501</v>
+        <v>-2.033921348696509</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-1.724059552221846</v>
+        <v>-1.71233652909045</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-3.071309211199399</v>
+        <v>-3.058455469786118</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.72561058807478</v>
+        <v>3.738095238095241</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.6223344365212071</v>
+        <v>-0.560677712380496</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.277273451186495</v>
+        <v>-1.240273145942517</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.447516641065029</v>
+        <v>2.508594574355826</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-5.638714376764085</v>
+        <v>-5.57628580507513</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-5.699714262946387</v>
+        <v>-5.613258414211927</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-8.454601352736226</v>
+        <v>-8.341848899788822</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-2.945068962768083</v>
+        <v>-2.83170363303919</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-4.815447710184564</v>
+        <v>-4.67829880043621</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-8.09284517827232</v>
+        <v>-7.93059958414289</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-8.795504798376989</v>
+        <v>-8.633935674508479</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-6.064866891638545</v>
+        <v>-6.081540396315553</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-7.676440504602802</v>
+        <v>-7.664717481471406</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-5.690356830247012</v>
+        <v>-5.677503088833731</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2.773229635693816</v>
+        <v>2.785714285714278</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-1.336620150806922</v>
+        <v>-1.274963426666211</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-2.229654403567444</v>
+        <v>-2.192654098323466</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>1.257040450588846</v>
+        <v>1.318118383879643</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-7.543476281525997</v>
+        <v>-7.481047709837043</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-8.794952358184482</v>
+        <v>-8.708496509450022</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-9.645077543212409</v>
+        <v>-9.532325090265005</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-3.897449915149032</v>
+        <v>-3.784084585420139</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-5.053542948279798</v>
+        <v>-4.916394038531443</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-8.795504798376989</v>
+        <v>-8.633935674508479</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that BB Width-20 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that BB Width-20 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3904,209 +3904,209 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 0.04388</t>
+          <t>X &lt; 0.04396</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2.268466441694791</v>
+        <v>2.251792937017782</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.724059552221846</v>
+        <v>-1.71233652909045</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.452500312610134</v>
+        <v>1.465354054023415</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.988675126210936</v>
+        <v>-1.976190476190474</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2.527096341283105</v>
+        <v>-2.465439617142394</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2.532250358337308</v>
+        <v>2.569250663581286</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8.399897593445985</v>
+        <v>8.460975526736782</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>9.123190385140681</v>
+        <v>9.185618956829636</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>11.44314287991075</v>
+        <v>11.5295987286452</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>11.78349388535902</v>
+        <v>11.89624633830643</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>13.95969294199381</v>
+        <v>14.0730582717227</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>15.18455228981544</v>
+        <v>15.3217011995638</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>14.76429767887054</v>
+        <v>14.92654327299997</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>15.01401901114683</v>
+        <v>15.17558813501534</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 0.06395</t>
+          <t>X &lt; 0.06403</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>224</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1.970847394075733</v>
+        <v>1.954173889398724</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.8057023525400595</v>
+        <v>0.8174253756714549</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.857262217372039</v>
+        <v>0.8701159587853198</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.244627507163322</v>
+        <v>-1.232142857142861</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.4437630079497836</v>
+        <v>-0.3821062838090725</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1463210702341229</v>
+        <v>-0.1093207649901444</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.6618023553507513</v>
+        <v>0.722880288641548</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.087476099426389</v>
+        <v>1.149904671115344</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1.472904784672657</v>
+        <v>1.559360633407117</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.069208171073299</v>
+        <v>1.181960624020704</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.86445484675572</v>
+        <v>0.9778201764846131</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.898838004101151</v>
+        <v>1.035986913849506</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>1.371440536013402</v>
+        <v>1.533686130142833</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>1.174733296861106</v>
+        <v>1.336302420729616</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 0.08403</t>
+          <t>X &lt; 0.0841</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.008507205081855</v>
+        <v>0.9782602681362675</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.0934316465923</v>
+        <v>3.077253725616082</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.893115469178589</v>
+        <v>2.877314186913779</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.634263543420332</v>
+        <v>2.813399778516057</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.512184740799526</v>
+        <v>1.742755288726926</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.560599441161109</v>
+        <v>3.565928404445081</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.864970782254588</v>
+        <v>3.892869214444424</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.175997500204602</v>
+        <v>4.39602870212309</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3.920445084839422</v>
+        <v>4.165257643373899</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>5.015845191640288</v>
+        <v>5.27941355868294</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>5.394749454871345</v>
+        <v>5.656668459984061</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>6.401895258131169</v>
+        <v>6.490028995798568</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>6.565298234734904</v>
+        <v>6.482467968459552</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>7.398677154559827</v>
+        <v>7.506706628924533</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 0.1041</t>
+          <t>X &lt; 0.1042</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1333944124163438</v>
+        <v>-0.2647668084576296</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1807023525400524</v>
+        <v>0.01404953464501091</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.6156309113842937</v>
+        <v>0.3870147226720277</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.07591704729213</v>
+        <v>0.8454858394617446</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.9775398366203873</v>
+        <v>0.7943527992765169</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.155069783136931</v>
+        <v>1.943370519628857</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.73040207246531</v>
+        <v>2.539888581553448</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4.463438695686015</v>
+        <v>4.374165350195305</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.402438809503714</v>
+        <v>4.337192741058509</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>4.652423635476886</v>
+        <v>4.608654412160284</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.667692313359524</v>
+        <v>4.733101040199216</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5.252130476205508</v>
+        <v>5.296638542922196</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>4.941886866360726</v>
+        <v>4.968882931146432</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>5.521641201937335</v>
+        <v>5.615148574575777</v>
       </c>
     </row>
     <row r="10">
@@ -4116,49 +4116,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.5165025706218387</v>
+        <v>-0.6248659232476399</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.518861891954117</v>
+        <v>-0.5686987461084101</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.03807315560871416</v>
+        <v>-0.1427646032755732</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2508345390412998</v>
+        <v>0.06908665105385836</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.4549875813948745</v>
+        <v>0.2355752150199777</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.247479024061029</v>
+        <v>1.16409843875693</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.740303062564323</v>
+        <v>1.67721284133475</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.758268178634303</v>
+        <v>2.768757130131739</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.119710536676436</v>
+        <v>2.122981282651232</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.424700863199661</v>
+        <v>2.413487717616768</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.302455789707167</v>
+        <v>2.339482343405621</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.584363699527842</v>
+        <v>2.610235034150264</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.154208098483934</v>
+        <v>3.168753737432652</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.733962434060544</v>
+        <v>3.796440100183609</v>
       </c>
     </row>
     <row r="11">
@@ -4168,153 +4168,153 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.302195564253765</v>
+        <v>-1.389035591703127</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.494187190906189</v>
+        <v>-2.618929935683866</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.468932864142204</v>
+        <v>-2.563949975280615</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.209730666415425</v>
+        <v>-2.241758241758241</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.038932023331562</v>
+        <v>-2.089981741684525</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.741490085615901</v>
+        <v>-1.688991094660466</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.761749270328536</v>
+        <v>-1.715725044447439</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.9394420179172585</v>
+        <v>-0.8638950721452474</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.064916436659203</v>
+        <v>-0.9944860497748209</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.7545000356136242</v>
+        <v>-0.690973639659056</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.8947788273715673</v>
+        <v>-0.7952620467583813</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.7314466049068642</v>
+        <v>-0.6371147592521638</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.4424813576957334</v>
+        <v>-0.3526398748245256</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.0006635722594765525</v>
+        <v>0.1258826858253528</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 0.1643</t>
+          <t>X &lt; 0.1644</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.118775247433689</v>
+        <v>-1.090722430136047</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.839639764889448</v>
+        <v>-1.84248505152194</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.044403035885232</v>
+        <v>-2.047348614175242</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.993817571958139</v>
+        <v>-1.996627835683633</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.262260385302447</v>
+        <v>-2.29674089771904</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-2.018814127932352</v>
+        <v>-1.995733224710861</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.725578082785624</v>
+        <v>-1.705729521752254</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.112847874655685</v>
+        <v>-1.067837264368528</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.227843441183559</v>
+        <v>-1.183329368898264</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.8360679782633227</v>
+        <v>-0.7940504477923085</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.040821302580902</v>
+        <v>-0.9684833853278292</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.6284683828164646</v>
+        <v>-0.5573012634903947</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.9407316330702216</v>
+        <v>-0.8686049749784672</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.9069930221762164</v>
+        <v>-0.805302603156953</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 0.1844</t>
+          <t>X &lt; 0.1845</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2131</v>
+        <v>2136</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.9939069237713625</v>
+        <v>-0.997780507995401</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.45616055014564</v>
+        <v>-1.439657625126635</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.107760564723925</v>
+        <v>-2.134907662214083</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.28140601490616</v>
+        <v>-2.306816668885638</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.397490298960037</v>
+        <v>-2.445459597162383</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.146974686913069</v>
+        <v>-2.148233344947499</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.903224124504455</v>
+        <v>-1.904444556368787</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.478807335580655</v>
+        <v>-1.458638746251602</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.586733547431649</v>
+        <v>-1.563971254228832</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.122921613735969</v>
+        <v>-1.101083434724281</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.656159217734455</v>
+        <v>-1.606832197789075</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.152512803702024</v>
+        <v>-1.10219296053242</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.572767414646925</v>
+        <v>-1.518406255711845</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.369972408039331</v>
+        <v>-1.290436477076696</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2337</v>
+        <v>2342</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.8061252061561532</v>
+        <v>-0.7479037569464353</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.156293984456283</v>
+        <v>-1.119627057876315</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.785045240027344</v>
+        <v>-1.745845427894302</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.188275924614139</v>
+        <v>-2.14625850340137</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.934150562201268</v>
+        <v>-1.932738233739187</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.807868230818507</v>
+        <v>-1.765095840977985</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.593072637008198</v>
+        <v>-1.547842815414889</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.418407512041306</v>
+        <v>-1.352224800775623</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.479407398223607</v>
+        <v>-1.408904324898316</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.302574945254094</v>
+        <v>-1.229438718324928</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.76406767907104</v>
+        <v>-1.666103064453551</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.729684521725609</v>
+        <v>-1.62734804470729</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.850409821587931</v>
+        <v>-1.743171988264592</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.600688489311644</v>
+        <v>-1.470745889627821</v>
       </c>
     </row>
     <row r="15">
@@ -4376,153 +4376,153 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2569</v>
+        <v>2572</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.6084791286048485</v>
+        <v>-0.5952182078657131</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.344514265989162</v>
+        <v>-1.34561089146699</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.485489352334028</v>
+        <v>-1.486639751628928</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.762623616112734</v>
+        <v>-1.762255173176939</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.7356080838548</v>
+        <v>-1.766190525797221</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.438166146139139</v>
+        <v>-1.434071595554926</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.05579203935536</v>
+        <v>-1.047601071797168</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.172644570094825</v>
+        <v>-1.143539859528566</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.350421412291134</v>
+        <v>-1.314793976050161</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.9549257331695955</v>
+        <v>-0.9143126679047597</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.587861229538547</v>
+        <v>-1.524260267343401</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.864883288230494</v>
+        <v>-1.794515916653317</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.012658335142696</v>
+        <v>-1.935374443950785</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.52938309083838</v>
+        <v>-1.431832438190618</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 0.2446</t>
+          <t>X &lt; 0.2447</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2752</v>
+        <v>2756</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.8430937427707335</v>
+        <v>-0.8308052160029078</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.020831962201811</v>
+        <v>-1.022479661487921</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.32383708260204</v>
+        <v>-1.324757292285987</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.646315960322369</v>
+        <v>-1.645646110938962</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.729697832297241</v>
+        <v>-1.754167766630047</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.55828120312448</v>
+        <v>-1.570712123270063</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.388654455280481</v>
+        <v>-1.395029850441233</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.310779714527101</v>
+        <v>-1.298502280369085</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.480791228616376</v>
+        <v>-1.460863664207622</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.313474553179191</v>
+        <v>-1.28698347535817</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.699913924008392</v>
+        <v>-1.652532435745485</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.956228441081564</v>
+        <v>-1.900923891081597</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.122122586910194</v>
+        <v>-2.058792754773485</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.799726836029251</v>
+        <v>-1.717424512714295</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 0.2647</t>
+          <t>X &lt; 0.2648</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2909</v>
+        <v>2914</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.932546381959547</v>
+        <v>-0.9214544965644649</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.050790931115209</v>
+        <v>-1.051593763084533</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.324460111106212</v>
+        <v>-1.324633735964376</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.691056078591892</v>
+        <v>-1.689564197772135</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.696094067477674</v>
+        <v>-1.716046462685952</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.827101629880652</v>
+        <v>-1.835755692143749</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.653057930461756</v>
+        <v>-1.672947950219907</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.467095918449168</v>
+        <v>-1.46995834258329</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.631224027388434</v>
+        <v>-1.625591404962186</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.553195207603707</v>
+        <v>-1.540060329665771</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.964204977435209</v>
+        <v>-1.931235115155523</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.239206488360658</v>
+        <v>-2.197405208431505</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.35007643103468</v>
+        <v>-2.299626783358768</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.134731173010721</v>
+        <v>-2.066298324441476</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3064</v>
+        <v>3070</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.7187720877124164</v>
+        <v>-0.7099172092528647</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.3916568843143011</v>
+        <v>-0.3943920897962485</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.8341914902107064</v>
+        <v>-0.8356150190975598</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.240553191648331</v>
+        <v>-1.240259740259745</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.076943407595778</v>
+        <v>-1.095174070196116</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.251180822354144</v>
+        <v>-1.259766323330425</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.351131692656715</v>
+        <v>-1.368094222709956</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.246074814411735</v>
+        <v>-1.263944483631086</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.535534230620136</v>
+        <v>-1.54357200306211</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.635006674133706</v>
+        <v>-1.634286239070661</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.035582452759378</v>
+        <v>-2.015996940339335</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.19702174972204</v>
+        <v>-2.168068145674297</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.160357300614727</v>
+        <v>-2.122347269866474</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.041184271210504</v>
+        <v>-1.98588231635739</v>
       </c>
     </row>
     <row r="19">
@@ -4584,101 +4584,101 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3220</v>
+        <v>3227</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.5727443920811055</v>
+        <v>-0.5656673804425338</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.370893556973428</v>
+        <v>-0.3730048717594201</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.059087087383965</v>
+        <v>-1.058984897122208</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.439394949023786</v>
+        <v>-1.437773070303194</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.279016464170979</v>
+        <v>-1.292621911568204</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.368285965407196</v>
+        <v>-1.374224717297494</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.250275324883354</v>
+        <v>-1.26382348377652</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.266218405385779</v>
+        <v>-1.280113887498942</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.527871612842866</v>
+        <v>-1.547959027130361</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.787934686069555</v>
+        <v>-1.798098623448013</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.054799811629373</v>
+        <v>-2.047389907548997</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.896193051799472</v>
+        <v>-1.879555270816248</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.974832755912068</v>
+        <v>-1.948124809846554</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.725111423635781</v>
+        <v>-1.682174492812372</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.3249</t>
+          <t>X &lt; 0.325</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3355</v>
+        <v>3363</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.5612147768092655</v>
+        <v>-0.5551355215694471</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.5219016150059304</v>
+        <v>-0.5229185396724674</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.25776285273929</v>
+        <v>-1.256440057812192</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.379446013560226</v>
+        <v>-1.377599423997289</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.128286817473587</v>
+        <v>-1.139393184334402</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.142312649360555</v>
+        <v>-1.147323477199315</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.06222555241748</v>
+        <v>-1.073431707967188</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.066604925298066</v>
+        <v>-1.078130354114691</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.171080401773793</v>
+        <v>-1.1881368216319</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.468581907700383</v>
+        <v>-1.49104204898196</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.762754009961327</v>
+        <v>-1.768126687109302</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.489920778100256</v>
+        <v>-1.485770674772866</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.701531573843965</v>
+        <v>-1.686332555095838</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.451810241567678</v>
+        <v>-1.420988051212944</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3452</v>
+        <v>3461</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.6736809545254019</v>
+        <v>-0.6678550603504263</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.5366790813972884</v>
+        <v>-0.5372854548168036</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.233984686013599</v>
+        <v>-1.232418603426666</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.406343320982344</v>
+        <v>-1.404103387249457</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.004057976139485</v>
+        <v>-1.01353897215818</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.8356574064463516</v>
+        <v>-0.8405421956206212</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.7601553166069266</v>
+        <v>-0.7703640679246107</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.7775745518037169</v>
+        <v>-0.7880099524785393</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.9096847595410864</v>
+        <v>-0.9247194094582696</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.106953344792814</v>
+        <v>-1.126841684781603</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.411658379531318</v>
+        <v>-1.430625880922172</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.17449422566213</v>
+        <v>-1.183393474748321</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.276092984926848</v>
+        <v>-1.273836358922118</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.142246507806988</v>
+        <v>-1.12440773735846</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3525</v>
+        <v>3536</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.6981315630711578</v>
+        <v>-0.6926984690120861</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.3719802589660901</v>
+        <v>-0.3728830475851126</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.8648028462771862</v>
+        <v>-0.8642470844302821</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.143821055550426</v>
+        <v>-1.14225284022239</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.6482128886662863</v>
+        <v>-0.6573934085320161</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.6751594459014854</v>
+        <v>-0.6797012874022599</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.6313359704978581</v>
+        <v>-0.6404719955405511</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.5449601611968404</v>
+        <v>-0.5546407834301164</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.6754931831854947</v>
+        <v>-0.6891718634662425</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.6881614434391707</v>
+        <v>-0.7066592307008506</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.8772114823787049</v>
+        <v>-0.8951867261916888</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.6569516401740216</v>
+        <v>-0.6800754296859779</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.7368772664337371</v>
+        <v>-0.7485647685202892</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.6415027720345279</v>
+        <v>-0.653435782243875</v>
       </c>
     </row>
     <row r="23">
@@ -4792,101 +4792,101 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3593</v>
+        <v>3605</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.5244976657451943</v>
+        <v>-0.5200620736432029</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.1244294089023867</v>
+        <v>-0.125912631358851</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.6153079427674939</v>
+        <v>-0.6153454824283315</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.6921365274242177</v>
+        <v>-0.691859316340647</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.4105473341177799</v>
+        <v>-0.4191645492846021</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.4867522996545119</v>
+        <v>-0.4911265457026417</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.5564516129032171</v>
+        <v>-0.5644951266408498</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.3973113415294378</v>
+        <v>-0.4061047445589878</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.5542630863668094</v>
+        <v>-0.5664308189078753</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.5551613432044675</v>
+        <v>-0.571592002349874</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.71666703469986</v>
+        <v>-0.7326644608292909</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.4721137145557108</v>
+        <v>-0.492786502919472</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.542960449756535</v>
+        <v>-0.5674746336635295</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.4446108644048365</v>
+        <v>-0.4693494516698209</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.4052</t>
+          <t>X &lt; 0.4053</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3665</v>
+        <v>3677</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.3727205388070374</v>
+        <v>-0.3691904156728896</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.0423908408263074</v>
+        <v>0.04062271912496129</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.4193583329155501</v>
+        <v>-0.4197817790516822</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.5737091398163798</v>
+        <v>-0.5735789840753327</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.2265027233242307</v>
+        <v>-0.2343464202326047</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2953331662241609</v>
+        <v>-0.2995223544454646</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.3925082577833976</v>
+        <v>-0.3997348812048926</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.3000885968416611</v>
+        <v>-0.3078064339620425</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.427883459780432</v>
+        <v>-0.4385345322637093</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.3909016291836807</v>
+        <v>-0.405340963280878</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.4714230158396902</v>
+        <v>-0.4856891402855723</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.1218484270025186</v>
+        <v>-0.1405750400976018</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.1994619657401699</v>
+        <v>-0.2214408798781449</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.2071854324314231</v>
+        <v>-0.229050739843828</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3747</v>
+        <v>3759</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.3125872563801835</v>
+        <v>-0.3096876467321579</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.005123741207256671</v>
+        <v>0.00376757364849567</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.3753463130012662</v>
+        <v>-0.3756210628137708</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.5500906426437524</v>
+        <v>-0.5497668953492791</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.2222127264953428</v>
+        <v>-0.2285576031903176</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1765189016969302</v>
+        <v>-0.180189967462745</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.1934758241149623</v>
+        <v>-0.1998493980286611</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.08658465197248688</v>
+        <v>-0.0934552226429588</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.1062529978433346</v>
+        <v>-0.115813952899245</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.1152378814079356</v>
+        <v>-0.1277846400163511</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.2250689627680842</v>
+        <v>-0.2373389334113298</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.04236536441616323</v>
+        <v>-0.05794707027325785</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.04741142312671798</v>
+        <v>-0.06585794280550061</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.1028363779263444</v>
+        <v>-0.1210333068574982</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3818</v>
+        <v>3830</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.2355422095339179</v>
+        <v>-0.2332447939215925</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.07253375873177248</v>
+        <v>0.07120874742722805</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2559527212542321</v>
+        <v>-0.2563578017681039</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.4250089073723089</v>
+        <v>-0.4248511904761969</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.06090997125560449</v>
+        <v>-0.06650140158527762</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.01563472096892582</v>
+        <v>0.01211525079189357</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.002530044275772525</v>
+        <v>-0.008252664930822107</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.1199028776690696</v>
+        <v>0.1136690089672783</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.02104853864298661</v>
+        <v>0.01286687293031008</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.04880000780799065</v>
+        <v>0.03806018434562475</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.03658078340840376</v>
+        <v>-0.04711366869446465</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.1695934266890404</v>
+        <v>0.1561777876938351</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.2092533516345441</v>
+        <v>0.1933516408263429</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.185761883256383</v>
+        <v>0.1699932077493997</v>
       </c>
     </row>
     <row r="27">
@@ -5000,101 +5000,101 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3885</v>
+        <v>3897</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.05629106520740379</v>
+        <v>-0.05486885813507314</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.1418446231511439</v>
+        <v>0.1405304811057917</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.162098298908397</v>
+        <v>-0.1625642576205948</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.1719381618488214</v>
+        <v>-0.1723463380745258</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.02261383554571239</v>
+        <v>0.01791931782943834</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.1543559691405889</v>
+        <v>0.1511054285346418</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.1350808753918571</v>
+        <v>0.1300816937937697</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.2730967624950082</v>
+        <v>0.2675705691425065</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.2006407376656796</v>
+        <v>0.1935317544439457</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.2133142578381708</v>
+        <v>0.2041893565801303</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.1001985269438492</v>
+        <v>0.09137329003773687</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.2262664285195513</v>
+        <v>0.2152636514745367</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.2837447783485132</v>
+        <v>0.2706757951725152</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.2907242878521075</v>
+        <v>0.2776813202493997</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.4855</t>
+          <t>X &lt; 0.4856</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3921</v>
+        <v>3933</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.0485037235114234</v>
+        <v>0.04944215382564465</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.2046753284581158</v>
+        <v>0.2032890367252307</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.04921939867215031</v>
+        <v>-0.04990722290114746</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.1340640373083275</v>
+        <v>-0.1344697655882072</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.07922863145407888</v>
+        <v>0.07496771778549061</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.1870516527415589</v>
+        <v>0.1840692375472841</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.1162684595113532</v>
+        <v>0.1119303248997028</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.3251257047230496</v>
+        <v>0.3200620714707654</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.303730415994977</v>
+        <v>0.2971626358739314</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.2830389263053377</v>
+        <v>0.2748159525885114</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.1181318527263073</v>
+        <v>0.1103695376925131</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.3453257503594926</v>
+        <v>0.3353152856048212</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.3984493507580567</v>
+        <v>0.3866347829135393</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.4076868072629765</v>
+        <v>0.3958852546259592</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3951</v>
+        <v>3963</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.1301741924035511</v>
+        <v>0.1307332455355521</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.2477511251149451</v>
+        <v>0.2463337314665992</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.01803960253104009</v>
+        <v>0.0172509073797471</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.09040508858215901</v>
+        <v>-0.09084534896264529</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.117203803017027</v>
+        <v>0.1133260280885011</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.2264732862050991</v>
+        <v>0.2236738027689711</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.1303290282735787</v>
+        <v>0.1264427211712302</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.33406442391464</v>
+        <v>0.3294839102183857</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.2870929978750283</v>
+        <v>0.281278836172099</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.3359591192401794</v>
+        <v>0.3284909275966328</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.09489057188037719</v>
+        <v>0.08811482384431457</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.2700208308873187</v>
+        <v>0.2613517129848049</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.3701392057646942</v>
+        <v>0.3597276466485226</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.4571256387636993</v>
+        <v>0.4464868048542101</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3983</v>
+        <v>3995</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.1091642823926264</v>
+        <v>0.1096486541549382</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.1377915712062432</v>
+        <v>0.1368084196302419</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.04319561222951762</v>
+        <v>-0.04369190085379415</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.2248741888562833</v>
+        <v>-0.22480827537008</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.001770917043067755</v>
+        <v>-0.001237152939935982</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.06240749761497</v>
+        <v>0.0604180023629155</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.04150160347105469</v>
+        <v>0.03840109966461114</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.2649015193311328</v>
+        <v>0.261064381187829</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.3181010878679587</v>
+        <v>0.3129320619785503</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.3095965762472659</v>
+        <v>0.3031694976676889</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.1189885719367112</v>
+        <v>0.1131021031622481</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.217712354343135</v>
+        <v>0.2103676994387058</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.3638387000983059</v>
+        <v>0.3548287012853919</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.4772376905342242</v>
+        <v>0.4679178328519171</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4001</v>
+        <v>4013</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.2220574446131423</v>
+        <v>0.2221286122714901</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.1685988318394678</v>
+        <v>0.1675806551745609</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.06143541207364223</v>
+        <v>0.06068681933629705</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.1188172354106385</v>
+        <v>-0.1190121089449931</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.0545447939739887</v>
+        <v>0.05166866824037442</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.09131389395360401</v>
+        <v>0.08941267018945354</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.09507865988454256</v>
+        <v>0.09210559070265845</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.3153897505369443</v>
+        <v>0.3116986497169876</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.3431262382066507</v>
+        <v>0.3382929380362896</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.3807829882660911</v>
+        <v>0.3746772924655275</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.1901291724300478</v>
+        <v>0.1845646272529748</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.2885814108318172</v>
+        <v>0.2816727348778016</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.4571655306589335</v>
+        <v>0.4486444901684479</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.5712011441849967</v>
+        <v>0.5623668185794628</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4017</v>
+        <v>4029</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1120207368619788</v>
+        <v>0.1123523017829839</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.1268073768282534</v>
+        <v>0.1259637501897828</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.006335456056824285</v>
+        <v>-0.00682887855555947</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1605388555616329</v>
+        <v>-0.1605595444416963</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.01485448477895801</v>
+        <v>-0.01726866971439023</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.07262302914475782</v>
+        <v>0.070931544008765</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.07603126759159551</v>
+        <v>0.07336874963546336</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.3184604394711386</v>
+        <v>0.3150223910657814</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.3458446866404046</v>
+        <v>0.3413653787856887</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.3799695310761422</v>
+        <v>0.374337798049261</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.189259395440871</v>
+        <v>0.1841693828338222</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.2625745412639162</v>
+        <v>0.2563150848102751</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.3790313772279319</v>
+        <v>0.3714209759421863</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.4686937862099469</v>
+        <v>0.4608414768584055</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4030</v>
+        <v>4042</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.09127600083875365</v>
+        <v>0.09161443898477728</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.07608653293166157</v>
+        <v>0.07543333958715692</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.01632821942244789</v>
+        <v>0.01581050603427059</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1617067150841081</v>
+        <v>-0.161683824566353</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.006534095293595499</v>
+        <v>0.004262161372011519</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.09469286877388328</v>
+        <v>0.09306018739081168</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.04828099932257857</v>
+        <v>0.04590537420059349</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.2884176256900233</v>
+        <v>0.2852801651864851</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.3155096704931495</v>
+        <v>0.3114124177976763</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.371566695048088</v>
+        <v>0.3663402582273392</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.2056046466211257</v>
+        <v>0.2008468407968209</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.2787983215614744</v>
+        <v>0.2729517294493462</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.3935282845337937</v>
+        <v>0.3864210158359143</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.4092689225257757</v>
+        <v>0.4021379335591959</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4054</v>
+        <v>4066</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.07602319933760526</v>
+        <v>0.07630641487765644</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1251897392310752</v>
+        <v>0.1244648908399455</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.08806523968797819</v>
+        <v>0.0874150933029938</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.06352514495859651</v>
+        <v>-0.06371793074443843</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.05134089135052733</v>
+        <v>0.04931352337761297</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.09151039913354708</v>
+        <v>0.09011467929066441</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.02024679197789681</v>
+        <v>0.01832765983160556</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.206934227505208</v>
+        <v>0.2044233351624953</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.2334853287897829</v>
+        <v>0.2301637003966235</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.3088054392560764</v>
+        <v>0.3044597465198322</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1672471985991066</v>
+        <v>0.1632992341681501</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.2155469361947056</v>
+        <v>0.2107305576196978</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.3024340184865295</v>
+        <v>0.2965949081118495</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.2948703748792951</v>
+        <v>0.2890727812102654</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4075</v>
+        <v>4087</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1484403490659574</v>
+        <v>0.1484247604788749</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.2380269706672138</v>
+        <v>0.2370355593399367</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1256700210221311</v>
+        <v>0.1249789581578398</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.02446226848523025</v>
+        <v>-0.02470448760417554</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.06256831988008571</v>
+        <v>0.06083456440521928</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1040638008340764</v>
+        <v>0.1028281971588214</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.05723176670372965</v>
+        <v>0.05552736799111813</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.2160597798968595</v>
+        <v>0.2138553185622101</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.2666722916754622</v>
+        <v>0.2637140756637848</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.2882044236562109</v>
+        <v>0.2845202496798223</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1708375273414475</v>
+        <v>0.1674813710357839</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.194538624305082</v>
+        <v>0.1905129942743358</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.2297399892588814</v>
+        <v>0.224977715270029</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.2480242696919603</v>
+        <v>0.2432241935983015</v>
       </c>
     </row>
   </sheetData>
